--- a/セリフ編集/キャラタイプ別/ヤンキー×お気楽.xlsx
+++ b/セリフ編集/キャラタイプ別/ヤンキー×お気楽.xlsx
@@ -262,7 +262,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H249"/>
+  <dimension ref="A1:H280"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="F78" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">引き分けか。ちょうどいいんじゃね?</t>
+          <t xml:space="preserve">決着つかずか。ちょうどいいんじゃね?</t>
         </is>
       </c>
     </row>
@@ -4324,7 +4324,7 @@
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="C127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">fresh.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
@@ -4349,14 +4349,14 @@
       </c>
       <c r="F127" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあいいや、ここまで来れただけでも上等だぜ</t>
+          <t xml:space="preserve">お、今日は体が軽ぃな。もう一本いこうぜ</t>
         </is>
       </c>
     </row>
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="C128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">heavy.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
@@ -4381,14 +4381,14 @@
       </c>
       <c r="F128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マジか、ここまで来ちゃったぜ！</t>
+          <t xml:space="preserve">体がだりぃわ。今日やっても、ザルに水だろ</t>
         </is>
       </c>
     </row>
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="C129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">warm.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
@@ -4413,14 +4413,14 @@
       </c>
       <c r="F129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おー、いい感じに仕上がってきたぜ</t>
+          <t xml:space="preserve">なんか今日、乗んねーな。ま、動けてるからいっか</t>
         </is>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">cap_reached.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
@@ -4445,14 +4445,14 @@
       </c>
       <c r="F130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うっひょー！ 最強じゃね？</t>
+          <t xml:space="preserve">まあいいや、ここまで来れただけでも上等だぜ</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">ovr_elite.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
@@ -4477,14 +4477,14 @@
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高だぜ！ もっと声出せ〜！</t>
+          <t xml:space="preserve">マジか、ここまで来ちゃったぜ！</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="C132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">ovr_growth.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
@@ -4509,14 +4509,14 @@
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんだろうな…楽しいって感覚、どこ行っちまったんだ</t>
+          <t xml:space="preserve">おー、いい感じに仕上がってきたぜ</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="C133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">ovr_legend.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
@@ -4541,14 +4541,14 @@
       </c>
       <c r="F133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おっし、やる気出てきたぜ！ 楽しまねーとな</t>
+          <t xml:space="preserve">うっひょー！ 最強じゃね？</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="C134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">pop_star.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
@@ -4573,14 +4573,14 @@
       </c>
       <c r="F134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いやー長かったな！ でもまた楽しくなってきたぜ</t>
+          <t xml:space="preserve">最高だぜ！ もっと声出せ〜！</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4590,12 +4590,12 @@
       </c>
       <c r="C135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
@@ -4605,14 +4605,14 @@
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんだろうな…いつもみたいに動かねーよ</t>
+          <t xml:space="preserve">なんだろうな…楽しいって感覚、どこ行っちまったんだ</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="C136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
@@ -4637,14 +4637,14 @@
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あれ、治ったはずなのに調子でねーな</t>
+          <t xml:space="preserve">おっし、やる気出てきたぜ！ 楽しまねーとな</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="C137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
@@ -4669,14 +4669,14 @@
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まいったな…リングがちょっと怖ぇーよ</t>
+          <t xml:space="preserve">いやー長かったな！ でもまた楽しくなってきたぜ</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">defeat.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
@@ -4701,14 +4701,14 @@
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">怪我は治ったんだけどな…なんか乗んねーわ</t>
+          <t xml:space="preserve">なんだろうな…いつもみたいに動かねーよ</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4718,29 +4718,29 @@
       </c>
       <c r="C139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">終わった瞬間「もう1ラウンドくれ！」って叫びそうになった！</t>
+          <t xml:space="preserve">あれ、治ったはずなのに調子でねーな</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4750,29 +4750,29 @@
       </c>
       <c r="C140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンの響き、たまんねえ！ もっと楽しむぜ！</t>
+          <t xml:space="preserve">まいったな…リングがちょっと怖ぇーよ</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4782,29 +4782,29 @@
       </c>
       <c r="C141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">penalty_end.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最っ高に楽しい選手人生だったぜ！ みんなありがとな！ プロレス最高！</t>
+          <t xml:space="preserve">怪我は治ったんだけどな…なんか乗んねーわ</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">bestMatch.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
@@ -4829,14 +4829,14 @@
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うおお！ MVP！ いい響きじゃん！</t>
+          <t xml:space="preserve">終わった瞬間「もう1ラウンドくれ！」って叫びそうになった！</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">champion.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
@@ -4861,14 +4861,14 @@
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うっそだろ！？ まあいいや、もらえるもんはもらっとく！</t>
+          <t xml:space="preserve">チャンピオンの響き、たまんねえ！ もっと楽しむぜ！</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="C144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">hallOfFame.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
@@ -4893,14 +4893,14 @@
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おーっ、ドームか。まぁやるだけよ</t>
+          <t xml:space="preserve">最っ高に楽しい選手人生だったぜ！ みんなありがとな！ プロレス最高！</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="C145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[2]</t>
+          <t xml:space="preserve">mvp.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
@@ -4925,14 +4925,14 @@
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんつーか、あんま緊張しねーな。やるべ</t>
+          <t xml:space="preserve">うおお！ MVP！ いい響きじゃん！</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.easygoing.delinquent[3]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4942,12 +4942,12 @@
       </c>
       <c r="C146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[3]</t>
+          <t xml:space="preserve">rookie.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
@@ -4957,14 +4957,14 @@
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いつも通りだろ。気楽に行こうぜ</t>
+          <t xml:space="preserve">うっそだろ！？ まあいいや、もらえるもんはもらっとく！</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="C147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D147" t="inlineStr" s="12">
@@ -4989,14 +4989,14 @@
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マジで満員かよ! やっべ、嬉しくて笑えてきたわ</t>
+          <t xml:space="preserve">おーっ、ドームか。まぁやるだけよ</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="C148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D148" t="inlineStr" s="12">
@@ -5021,14 +5021,14 @@
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">観客全員ぶち上がってたな! 気持ち良かったぜ</t>
+          <t xml:space="preserve">なんつーか、あんま緊張しねーな。やるべ</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.easygoing.delinquent[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.easygoing.delinquent[3]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5038,7 +5038,7 @@
       </c>
       <c r="C149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D149" t="inlineStr" s="12">
@@ -5053,14 +5053,14 @@
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こういう日もあんだな、人生ってよ</t>
+          <t xml:space="preserve">いつも通りだろ。気楽に行こうぜ</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5070,29 +5070,29 @@
       </c>
       <c r="C150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんか急にキタわ！掴めた感じ！</t>
+          <t xml:space="preserve">マジで満員かよ! やっべ、嬉しくて笑えてきたわ</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5102,29 +5102,29 @@
       </c>
       <c r="C151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あいつ最高！一緒だとテンション上がるわ！</t>
+          <t xml:space="preserve">観客全員ぶち上がってたな! 気持ち良かったぜ</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.easygoing.delinquent[3]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5134,29 +5134,29 @@
       </c>
       <c r="C152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">easygoing.delinquent[3]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あー疲れた。ちょい休むわ</t>
+          <t xml:space="preserve">こういう日もあんだな、人生ってよ</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">N1.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
@@ -5181,14 +5181,14 @@
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンが盛り上がってんの最高じゃん！</t>
+          <t xml:space="preserve">なんか急にキタわ！掴めた感じ！</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">N2.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
@@ -5213,14 +5213,14 @@
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もーいいわ。考えさせてくれ</t>
+          <t xml:space="preserve">あいつ最高！一緒だとテンション上がるわ！</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5235,7 +5235,7 @@
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">N3.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
@@ -5245,14 +5245,14 @@
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あー…いや、なんでもねー。平気平気</t>
+          <t xml:space="preserve">あー疲れた。ちょい休むわ</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5262,29 +5262,29 @@
       </c>
       <c r="C156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">N4.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やった！ラッキー！</t>
+          <t xml:space="preserve">ファンが盛り上がってんの最高じゃん！</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5294,29 +5294,29 @@
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">N5_low.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">合宿だー！ 盛り上がっていくぞー！</t>
+          <t xml:space="preserve">もーいいわ。考えさせてくれ</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5326,29 +5326,29 @@
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">N5_warning.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見てくれてたんだ？ じゃ、もうちょいやるか！</t>
+          <t xml:space="preserve">あー…いや、なんでもねー。平気平気</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">bonus.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
@@ -5373,14 +5373,14 @@
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おっしゃ！元気出た！やってやるわ！</t>
+          <t xml:space="preserve">やった！ラッキー！</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">camp.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
@@ -5405,14 +5405,14 @@
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テレビ！？ みんな見てるー？</t>
+          <t xml:space="preserve">合宿だー！ 盛り上がっていくぞー！</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5427,7 +5427,7 @@
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">encourage_high_trust.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
@@ -5437,14 +5437,14 @@
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うぇーい！飲むぞ〜！</t>
+          <t xml:space="preserve">見てくれてたんだ？ じゃ、もうちょいやるか！</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5459,7 +5459,7 @@
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">encourage.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
@@ -5469,14 +5469,14 @@
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">バカンスだー！戻ったら本気出すから！</t>
+          <t xml:space="preserve">おっしゃ！元気出た！やってやるわ！</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">faction_decree.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
@@ -5501,14 +5501,14 @@
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マジか！すぐ治してくる！</t>
+          <t xml:space="preserve">えー。せっかく楽しくやってたのに</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">media.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
@@ -5533,14 +5533,14 @@
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マンツーマン！？ 超贅沢じゃん！</t>
+          <t xml:space="preserve">テレビ！？ みんな見てるー？</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5550,12 +5550,12 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">party.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
@@ -5565,14 +5565,14 @@
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テレビ出んの！？ 最高じゃん！</t>
+          <t xml:space="preserve">うぇーい！飲むぞ〜！</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5582,12 +5582,12 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">refresh_leave.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
@@ -5597,14 +5597,14 @@
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">他所から話来たんだけど！ちょっと嬉しくね？</t>
+          <t xml:space="preserve">バカンスだー！戻ったら本気出すから！</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5614,12 +5614,12 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">special_treatment.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
@@ -5629,14 +5629,14 @@
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">タイトルマッチ組めよ！やる気あんだからさ！</t>
+          <t xml:space="preserve">マジか！すぐ治してくる！</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5646,12 +5646,12 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">trainer.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
@@ -5661,14 +5661,14 @@
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あいつとやらせろよ！ケリつけてやる！</t>
+          <t xml:space="preserve">マンツーマン！？ 超贅沢じゃん！</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5683,7 +5683,7 @@
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">E1.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
@@ -5693,14 +5693,14 @@
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">無理！限界！休ませて！</t>
+          <t xml:space="preserve">テレビ出んの！？ 最高じゃん！</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">E6.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
@@ -5725,14 +5725,14 @@
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう無理！ちゃんと話し合えよ！</t>
+          <t xml:space="preserve">他所から話来たんだけど！ちょっと嬉しくね？</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5747,7 +5747,7 @@
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">S_boycott.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
@@ -5757,14 +5757,14 @@
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">特訓すんぞ！もっと強くなりてーんだよ！</t>
+          <t xml:space="preserve">はは…今日はサボるわ…</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">S_boycott.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
@@ -5789,14 +5789,14 @@
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">後輩の面倒見るわ！任せとけ！</t>
+          <t xml:space="preserve">練習な…うーん、今日はパスで</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">S_grumble.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
@@ -5821,14 +5821,14 @@
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いった！やっちまったけど、すぐ治すから！</t>
+          <t xml:space="preserve">（いつもの軽口が消え、「なぁ、ちょっとさぁ…」と珍しく愚痴をこぼしている）</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">S_sns.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -5853,14 +5853,14 @@
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あいつマジ無理！もう顔も見たくねえ！</t>
+          <t xml:space="preserve">（SNSに「最近ちょい考えることあってさ」と珍しく真面目な投稿）</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5870,12 +5870,12 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">S1.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -5885,14 +5885,14 @@
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やんのか！？ 売られたケンカは買うぜ！</t>
+          <t xml:space="preserve">タイトルマッチ組めよ！やる気あんだからさ！</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">S2.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -5917,14 +5917,14 @@
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">コラボか。なんか面白そうじゃん</t>
+          <t xml:space="preserve">あいつとやらせろよ！ケリつけてやる！</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">S3.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -5949,14 +5949,14 @@
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">CM撮影！？ 楽しそうじゃん！</t>
+          <t xml:space="preserve">無理！限界！休ませて！</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5966,12 +5966,12 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">S4_direct.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -5981,14 +5981,14 @@
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンと直接会えるのいいじゃん！ 楽しみ！</t>
+          <t xml:space="preserve">もう無理！ちゃんと話し合えよ！</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">S4_silent.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -6013,14 +6013,14 @@
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ランウェイか。めっちゃ目立てそうじゃん！</t>
+          <t xml:space="preserve">あー…いや、なんでもねえって（笑ってはいるが、目が笑っていない）</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">S5.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6045,14 +6045,14 @@
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">グラビアか。まぁ、派手にやってやる</t>
+          <t xml:space="preserve">特訓すんぞ！もっと強くなりてーんだよ！</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6062,12 +6062,12 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">S6.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6077,14 +6077,14 @@
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テレビで暴れてやる！ 楽しみ！</t>
+          <t xml:space="preserve">後輩の面倒見るわ！任せとけ！</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6099,7 +6099,7 @@
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">B1.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6109,14 +6109,14 @@
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テレビ！？ マジ！？ やったー！</t>
+          <t xml:space="preserve">いった！やっちまったけど、すぐ治すから！</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6126,29 +6126,29 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">B2_fighter1.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しくやろうぜ！退屈なのは嫌いだからな！</t>
+          <t xml:space="preserve">あいつマジ無理！もう顔も見たくねえ！</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6158,29 +6158,29 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">B2_fighter2.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よっ、よろしくな! 楽しくやろうぜ</t>
+          <t xml:space="preserve">やんのか！？ 売られたケンカは買うぜ！</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6190,29 +6190,29 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">B4_brand.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よっしゃー！新天地だ！暴れるぞ！</t>
+          <t xml:space="preserve">コラボか。なんか面白そうじゃん</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6222,29 +6222,29 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">B4_cm.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よっしゃー！楽しくやろうぜ！</t>
+          <t xml:space="preserve">CM撮影！？ 楽しそうじゃん！</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6254,29 +6254,29 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">B4_fan.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やっちまったぜ〜 まぁすぐ戻るわ</t>
+          <t xml:space="preserve">ファンと直接会えるのいいじゃん！ 楽しみ！</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6286,29 +6286,29 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">B4_fashion.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しくやろうぜ！退屈なのは嫌いだからな！</t>
+          <t xml:space="preserve">ランウェイか。めっちゃ目立てそうじゃん！</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6318,29 +6318,29 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">B4_gravure.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よっ、よろしくな! 楽しくやろうぜ</t>
+          <t xml:space="preserve">グラビアか。まぁ、派手にやってやる</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6350,29 +6350,29 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">B4_variety.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よっしゃー！新天地だ！暴れるぞ！</t>
+          <t xml:space="preserve">テレビで暴れてやる！ 楽しみ！</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6382,29 +6382,29 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">B4.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よっしゃー！楽しくやろうぜ！</t>
+          <t xml:space="preserve">テレビ！？ マジ！？ やったー！</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6414,12 +6414,12 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6429,14 +6429,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やっちまったぜ〜 まぁすぐ戻るわ</t>
+          <t xml:space="preserve">楽しくやろうぜ！退屈なのは嫌いだからな！</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6446,12 +6446,12 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6461,14 +6461,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ、こんなもんか。元気でやれよ〜</t>
+          <t xml:space="preserve">よっ、よろしくな! 楽しくやろうぜ</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6478,12 +6478,12 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6493,14 +6493,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おじゃまー！暴れさせてもらうぜ！</t>
+          <t xml:space="preserve">よっしゃー！新天地だ！暴れるぞ！</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6525,14 +6525,14 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそー！悔しい！でも次やってやるからな！</t>
+          <t xml:space="preserve">よっしゃー！楽しくやろうぜ！</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6557,14 +6557,14 @@
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだまだ渡さねーよ！最高！</t>
+          <t xml:space="preserve">やっちまったぜ〜 まぁすぐ戻るわ</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6579,7 +6579,7 @@
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">draftInterest.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6589,14 +6589,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそー！でもまだ終わってねえから！</t>
+          <t xml:space="preserve">楽しくやろうぜ！退屈なのは嫌いだからな！</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">draftJoin.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6621,14 +6621,14 @@
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンだぜー！最高だろ！</t>
+          <t xml:space="preserve">よっ、よろしくな! 楽しくやろうぜ</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">faGreeting.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6653,14 +6653,14 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ、こんなもんか。元気でやれよ〜</t>
+          <t xml:space="preserve">フリーもそろそろ飽きたんでな。世話になるぜ</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">faSigning.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6685,14 +6685,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おじゃまー！暴れさせてもらうぜ！</t>
+          <t xml:space="preserve">よっしゃー！新天地だ！暴れるぞ！</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">faWelcome.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6717,14 +6717,14 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそー！悔しい！でも次やってやるからな！</t>
+          <t xml:space="preserve">よっしゃー！楽しくやろうぜ！</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6749,14 +6749,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだまだ渡さねーよ！最高！</t>
+          <t xml:space="preserve">お、今日は体が軽ぃな。もう一本いこうぜ</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6766,12 +6766,12 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">heatSelf.heavy.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6781,14 +6781,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそー！でもまだ終わってねえから！</t>
+          <t xml:space="preserve">体がだりぃわ。今日やっても、ザルに水だろ</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">heatSelf.warm.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6813,14 +6813,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンだぜー！最高だろ！</t>
+          <t xml:space="preserve">なんか今日、乗んねーな。ま、動けてるからいっか</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6830,29 +6830,29 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">injury.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">つるんでると楽しいんだわ、まじで</t>
+          <t xml:space="preserve">やっちまったぜ〜 まぁすぐ戻るわ</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6862,29 +6862,29 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">release.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一生の仲間だぜ。間違いない</t>
+          <t xml:space="preserve">まぁ、こんなもんか。元気でやれよ〜</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6894,29 +6894,29 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">rentalGreeting.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やり合うの、ワクワクすんだよな</t>
+          <t xml:space="preserve">おじゃまー！暴れさせてもらうぜ！</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6926,29 +6926,29 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">scoutGreeting.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">終わっちまったかー。まぁ次また来るっしょ</t>
+          <t xml:space="preserve">スカウトってのも、けっこう悪い気しねーな。やる気出てきたっ！</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6958,29 +6958,29 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いやー身体ガタガタだわ。でも最後だし、暴れて終わろうぜ</t>
+          <t xml:space="preserve">くそー！悔しい！でも次やってやるからな！</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -6990,29 +6990,29 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">titleDefense.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで残っちまったな。ま、痛いのは後で考えるわ</t>
+          <t xml:space="preserve">まだまだ渡さねーよ！最高！</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7022,29 +7022,29 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">titleLoss.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手は誰だ? ま、来た奴から順にぶっ倒すだけだ</t>
+          <t xml:space="preserve">くそー！でもまだ終わってねえから！</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7054,29 +7054,29 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">titleWin.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いいぜいいぜ、次々来いよ。まとめて相手してやるって</t>
+          <t xml:space="preserve">チャンピオンだぜー！最高だろ！</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7086,29 +7086,29 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人ぶっ倒したー! …はぁ、まだいけるっしょ。次、出てこいよー</t>
+          <t xml:space="preserve">まぁ、こんなもんか。元気でやれよ〜</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7118,29 +7118,29 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふう、一丁上がり。でもまだ終わってねえぞ。次、さっさと来い</t>
+          <t xml:space="preserve">おじゃまー！暴れさせてもらうぜ！</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7150,29 +7150,29 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で勝ったぜ！ いやー、最高の気分だな</t>
+          <t xml:space="preserve">くそー！悔しい！でも次やってやるからな！</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7182,29 +7182,29 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間がいたから全然余裕だったっての。まあ、ちょっとは焦ったけどな</t>
+          <t xml:space="preserve">まだまだ渡さねーよ！最高！</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7214,29 +7214,29 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVPねえ。まあもらっとくけどさ、一人じゃ盛り上がんねえよ</t>
+          <t xml:space="preserve">くそー！でもまだ終わってねえから！</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7246,29 +7246,29 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次は全員で暴れて、全員で勝つ。そうじゃなきゃつまんねえ</t>
+          <t xml:space="preserve">チャンピオンだぜー！最高だろ！</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7278,29 +7278,29 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">bond_39_down.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いやー次から次に来んのな。途中から面白くなっちゃったよ</t>
+          <t xml:space="preserve">う〜ん、ちょい合わねぇかもな…</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7310,29 +7310,29 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">bond_59_down.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人だっけ？ まあいいや、全員倒したし。あたしの勝ちってことで</t>
+          <t xml:space="preserve">あれ〜、最近ちょい素っ気なくね？</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7342,29 +7342,29 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">bond_59_down.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いえ〜い！ 優勝〜！ 最高じゃん！</t>
+          <t xml:space="preserve">んー、なんか空気変わった気ぃすんだけど</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7374,29 +7374,29 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">bond_60_up.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ひゃっほ〜！ やったぜ〜！</t>
+          <t xml:space="preserve">つるんでると楽しいんだわ、まじで</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7406,29 +7406,29 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">bond_80_up.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マジかー、負けたわ。ま、次があるし</t>
+          <t xml:space="preserve">一生の仲間だぜ。間違いない</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7438,29 +7438,29 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">rivalry_29_down.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">しゃーねえな。次だ次</t>
+          <t xml:space="preserve">熱い関係も一段落かぁ。ちっと寂しいな</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7470,29 +7470,29 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">rivalry_29_down.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いえーい！ 楽勝楽勝〜</t>
+          <t xml:space="preserve">まぁ因縁も永遠じゃねぇよな〜</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7502,29 +7502,29 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">rivalry_30_up.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ノリノリだぜ！ 次も行くぞ〜</t>
+          <t xml:space="preserve">やり合うの、ワクワクすんだよな</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7534,29 +7534,29 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">rivalry_50_up.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しかったぜ〜。またやりてえな</t>
+          <t xml:space="preserve">本気でやり合いてぇ相手なんて、そうはいねぇよ</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7566,29 +7566,29 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">rivalry_50_up.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあまあ良かったんじゃね？</t>
+          <t xml:space="preserve">へへ、考えると自然に気合入るんだわ</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7598,29 +7598,29 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">rivalry_70_up.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うっひょ〜決勝じゃん！ やるっきゃねえ！</t>
+          <t xml:space="preserve">この試合が一番楽しいんだわ。ずっと続けばいいのにな</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7630,29 +7630,29 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">rivalry_70_up.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最後だし、全力で暴れるぜ！</t>
+          <t xml:space="preserve">運命のライバルってやつだろ。最高だぜ</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7662,29 +7662,29 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">trust_above_75.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よーし、パパッとやっちまうか</t>
+          <t xml:space="preserve">ここ最高〜！ みんなとやんの楽しいわ！</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7694,29 +7694,29 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">trust_above_75.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">気楽にいこうぜ。でも手は抜かねえけど</t>
+          <t xml:space="preserve">この団体、すげぇ居心地いいんだわ〜</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7726,29 +7726,29 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">trust_below_20.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マジ？ ウケる。まあ出てやるよ</t>
+          <t xml:space="preserve">さすがにこれは…笑えねぇかも</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7758,29 +7758,29 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">trust_below_20.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、暴れる場所があるなら出るっしょ</t>
+          <t xml:space="preserve">あはは…って笑ってる場合じゃねぇよな、これ</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7790,29 +7790,29 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">trust_below_35.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高だぜ！楽しもうや！</t>
+          <t xml:space="preserve">う〜ん、最近ちっとモヤモヤすんだよなぁ…</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7822,29 +7822,29 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[2]</t>
+          <t xml:space="preserve">trust_below_35.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">へぇ、派手な舞台じゃん！せっかくだし楽しもっかな！</t>
+          <t xml:space="preserve">まぁ大丈夫…だよな？ ちょい不安だけど</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="12">
@@ -7864,19 +7864,19 @@
       </c>
       <c r="E237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マジかよ……！ やべえ、勝っちまった……！ 最高だ！</t>
+          <t xml:space="preserve">終わっちまったかー。まぁ次また来るっしょ</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7886,12 +7886,12 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">preFinal.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7901,14 +7901,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よう、暇だから殴りに来たぜ</t>
+          <t xml:space="preserve">いやー身体ガタガタだわ。でも最後だし、暴れて終わろうぜ</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[2]</t>
+          <t xml:space="preserve">preFinal.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7933,14 +7933,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">面白えことしようぜ。対抗戦だ対抗戦</t>
+          <t xml:space="preserve">ここまで残っちまったな。ま、痛いのは後で考えるわ</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7950,12 +7950,12 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">preMatch.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -7965,14 +7965,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">は？ 逃げんの？ ダッセー</t>
+          <t xml:space="preserve">相手は誰だ? ま、来た奴から順にぶっ倒すだけだ</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -7982,12 +7982,12 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[2]</t>
+          <t xml:space="preserve">preMatch.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -7997,14 +7997,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、ビビるのもわかるけどな。またな</t>
+          <t xml:space="preserve">いいぜいいぜ、次々来いよ。まとめて相手してやるって</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8014,12 +8014,12 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">survivor.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8029,14 +8029,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、こういう日もあるっしょ。次だ次！</t>
+          <t xml:space="preserve">一人ぶっ倒したー! …はぁ、まだいけるっしょ。次、出てこいよー</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8046,12 +8046,12 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">survivor.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8061,14 +8061,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くっそー、やられた。次は倍返しだ</t>
+          <t xml:space="preserve">ふう、一丁上がり。でもまだ終わってねえぞ。次、さっさと来い</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">champion.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8093,14 +8093,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いえーい！ 圧勝だぜ〜！</t>
+          <t xml:space="preserve">三人で勝ったぜ！ いやー、最高の気分だな</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">champion.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8125,14 +8125,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">面白かったぜ！ またかかって来いよ</t>
+          <t xml:space="preserve">仲間がいたから全然余裕だったっての。まあ、ちょっとは焦ったけどな</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">defiant.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8157,14 +8157,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よっしゃあ！ 勝った勝った！ 打ち上げだ打ち上げ！</t>
+          <t xml:space="preserve">MVPねえ。まあもらっとくけどさ、一人じゃ盛り上がんねえよ</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8174,12 +8174,12 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[2]</t>
+          <t xml:space="preserve">defiant.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8189,14 +8189,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よっしゃ〜！ まだまだいけるぜ〜！</t>
+          <t xml:space="preserve">次は全員で暴れて、全員で勝つ。そうじゃなきゃつまんねえ</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.easygoing.delinquent[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8206,12 +8206,12 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[3]</t>
+          <t xml:space="preserve">gauntlet.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8221,44 +8221,1036 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いえーい！ 圧勝〜！ 打ち上げ行くぞ〜！</t>
+          <t xml:space="preserve">いやー次から次に来んのな。途中から面白くなっちゃったよ</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.easygoing.delinquent[2]</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.easygoing.delinquent[2]</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">何人だっけ？ まあいいや、全員倒したし。あたしの勝ちってことで</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="40" customHeight="1">
+      <c r="A250" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.easygoing.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.easygoing.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">いえ〜い！ 優勝〜！ 最高じゃん！</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="40" customHeight="1">
+      <c r="A251" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.easygoing.delinquent[2]</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.easygoing.delinquent[2]</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ひゃっほ〜！ やったぜ〜！</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="40" customHeight="1">
+      <c r="A252" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.easygoing.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postLose.easygoing.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">マジかー、負けたわ。ま、次があるし</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="40" customHeight="1">
+      <c r="A253" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.easygoing.delinquent[2]</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postLose.easygoing.delinquent[2]</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">しゃーねえな。次だ次</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="40" customHeight="1">
+      <c r="A254" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.easygoing.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postMatchWin.easygoing.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">いえーい！ 楽勝楽勝〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="255" ht="40" customHeight="1">
+      <c r="A255" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.easygoing.delinquent[2]</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postMatchWin.easygoing.delinquent[2]</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ノリノリだぜ！ 次も行くぞ〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="40" customHeight="1">
+      <c r="A256" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.easygoing.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postWin.easygoing.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">楽しかったぜ〜。またやりてえな</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" ht="40" customHeight="1">
+      <c r="A257" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.easygoing.delinquent[2]</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postWin.easygoing.delinquent[2]</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まあまあ良かったんじゃね？</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" ht="40" customHeight="1">
+      <c r="A258" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.easygoing.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.easygoing.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">うっひょ〜決勝じゃん！ やるっきゃねえ！</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="40" customHeight="1">
+      <c r="A259" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.easygoing.delinquent[2]</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.easygoing.delinquent[2]</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">最後だし、全力で暴れるぜ！</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="40" customHeight="1">
+      <c r="A260" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.easygoing.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.easygoing.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">よーし、パパッとやっちまうか</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="40" customHeight="1">
+      <c r="A261" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.easygoing.delinquent[2]</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.easygoing.delinquent[2]</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">気楽にいこうぜ。でも手は抜かねえけど</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" ht="40" customHeight="1">
+      <c r="A262" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.easygoing.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">summon.easygoing.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">マジ？ ウケる。まあ出てやるよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" ht="40" customHeight="1">
+      <c r="A263" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.easygoing.delinquent[2]</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">summon.easygoing.delinquent[2]</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ま、暴れる場所があるなら出るっしょ</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="40" customHeight="1">
+      <c r="A264" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.easygoing.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">最高だぜ！楽しもうや！</t>
+        </is>
+      </c>
+    </row>
+    <row r="265" ht="40" customHeight="1">
+      <c r="A265" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.easygoing.delinquent[2]</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.delinquent[2]</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">へぇ、派手な舞台じゃん！せっかくだし楽しもっかな！</t>
+        </is>
+      </c>
+    </row>
+    <row r="266" ht="40" customHeight="1">
+      <c r="A266" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.easygoing.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">マジかよ……！ やべえ、勝っちまった……！ 最高だ！</t>
+        </is>
+      </c>
+    </row>
+    <row r="267" ht="40" customHeight="1">
+      <c r="A267" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.easygoing.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">よう、暇だから殴りに来たぜ</t>
+        </is>
+      </c>
+    </row>
+    <row r="268" ht="40" customHeight="1">
+      <c r="A268" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.easygoing.delinquent[2]</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.delinquent[2]</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">面白えことしようぜ。対抗戦だ対抗戦</t>
+        </is>
+      </c>
+    </row>
+    <row r="269" ht="40" customHeight="1">
+      <c r="A269" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.easygoing.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">は？ 逃げんの？ ダッセー</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="40" customHeight="1">
+      <c r="A270" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.easygoing.delinquent[2]</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.delinquent[2]</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ま、ビビるのもわかるけどな。またな</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="40" customHeight="1">
+      <c r="A271" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.easygoing.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.easygoing.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ま、こういう日もあるっしょ。次だ次！</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="40" customHeight="1">
+      <c r="A272" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.easygoing.delinquent[2]</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.easygoing.delinquent[2]</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">くっそー、やられた。次は倍返しだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="40" customHeight="1">
+      <c r="A273" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.easygoing.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.easygoing.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">いえーい！ 圧勝だぜ〜！</t>
+        </is>
+      </c>
+    </row>
+    <row r="274" ht="40" customHeight="1">
+      <c r="A274" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.easygoing.delinquent[2]</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.easygoing.delinquent[2]</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">面白かったぜ！ またかかって来いよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="275" ht="40" customHeight="1">
+      <c r="A275" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.easygoing.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">よっしゃあ！ 勝った勝った！ 打ち上げだ打ち上げ！</t>
+        </is>
+      </c>
+    </row>
+    <row r="276" ht="40" customHeight="1">
+      <c r="A276" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.easygoing.delinquent[2]</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.delinquent[2]</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">よっしゃ〜！ まだまだいけるぜ〜！</t>
+        </is>
+      </c>
+    </row>
+    <row r="277" ht="40" customHeight="1">
+      <c r="A277" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.easygoing.delinquent[3]</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.delinquent[3]</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">いえーい！ 圧勝〜！ 打ち上げ行くぞ〜！</t>
+        </is>
+      </c>
+    </row>
+    <row r="278" ht="40" customHeight="1">
+      <c r="A278" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">ENDING_LINES.fighter.easygoing.delinquent[1]</t>
         </is>
       </c>
-      <c r="B249" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr" s="2">
+      <c r="B278" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr" s="12">
+      <c r="D278" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fighter.easygoing.delinquent[1]</t>
         </is>
       </c>
-      <c r="E249" t="inlineStr" s="2">
+      <c r="E278" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
-      <c r="F249" t="inlineStr" s="3">
+      <c r="F278" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">最高だぜ！みんなありがとな！</t>
         </is>
       </c>
     </row>
+    <row r="279" ht="40" customHeight="1">
+      <c r="A279" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.easygoing.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">フリーもそろそろ飽きたんでな。世話になるぜ</t>
+        </is>
+      </c>
+    </row>
+    <row r="280" ht="40" customHeight="1">
+      <c r="A280" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.easygoing.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">スカウトってのも、けっこう悪い気しねーな。やる気出てきたっ！</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H249"/>
+  <autoFilter ref="A1:H280"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/ヤンキー×お気楽.xlsx
+++ b/セリフ編集/キャラタイプ別/ヤンキー×お気楽.xlsx
@@ -262,7 +262,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H280"/>
+  <dimension ref="A1:H321"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -320,7 +320,7 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
@@ -335,7 +335,7 @@
       </c>
       <c r="D2" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">atk.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr" s="2">
@@ -352,7 +352,7 @@
     <row r="3" ht="40" customHeight="1">
       <c r="A3" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
@@ -367,7 +367,7 @@
       </c>
       <c r="D3" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">atk.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr" s="2">
@@ -384,7 +384,7 @@
     <row r="4" ht="40" customHeight="1">
       <c r="A4" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.easygoing.delinquent[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.delinquent.easygoing[3]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
@@ -399,7 +399,7 @@
       </c>
       <c r="D4" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.easygoing.delinquent[3]</t>
+          <t xml:space="preserve">atk.delinquent.easygoing[3]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr" s="2">
@@ -416,7 +416,7 @@
     <row r="5" ht="40" customHeight="1">
       <c r="A5" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.easygoing.delinquent[4]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.delinquent.easygoing[4]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
@@ -431,7 +431,7 @@
       </c>
       <c r="D5" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.easygoing.delinquent[4]</t>
+          <t xml:space="preserve">atk.delinquent.easygoing[4]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr" s="2">
@@ -448,7 +448,7 @@
     <row r="6" ht="40" customHeight="1">
       <c r="A6" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
@@ -463,7 +463,7 @@
       </c>
       <c r="D6" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">bigmove.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr" s="2">
@@ -480,7 +480,7 @@
     <row r="7" ht="40" customHeight="1">
       <c r="A7" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
@@ -495,7 +495,7 @@
       </c>
       <c r="D7" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">bigmove.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr" s="2">
@@ -512,7 +512,7 @@
     <row r="8" ht="40" customHeight="1">
       <c r="A8" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.easygoing.delinquent[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.delinquent.easygoing[3]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
@@ -527,7 +527,7 @@
       </c>
       <c r="D8" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.easygoing.delinquent[3]</t>
+          <t xml:space="preserve">bigmove.delinquent.easygoing[3]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr" s="2">
@@ -544,7 +544,7 @@
     <row r="9" ht="40" customHeight="1">
       <c r="A9" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
@@ -559,7 +559,7 @@
       </c>
       <c r="D9" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">climax.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr" s="2">
@@ -576,7 +576,7 @@
     <row r="10" ht="40" customHeight="1">
       <c r="A10" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
@@ -591,7 +591,7 @@
       </c>
       <c r="D10" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">climax.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr" s="2">
@@ -608,7 +608,7 @@
     <row r="11" ht="40" customHeight="1">
       <c r="A11" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
@@ -623,7 +623,7 @@
       </c>
       <c r="D11" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr" s="2">
@@ -640,7 +640,7 @@
     <row r="12" ht="40" customHeight="1">
       <c r="A12" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
@@ -655,7 +655,7 @@
       </c>
       <c r="D12" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[2]</t>
+          <t xml:space="preserve">delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr" s="2">
@@ -672,7 +672,7 @@
     <row r="13" ht="40" customHeight="1">
       <c r="A13" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.easygoing.delinquent[3]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.delinquent.easygoing[3]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
@@ -687,7 +687,7 @@
       </c>
       <c r="D13" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[3]</t>
+          <t xml:space="preserve">delinquent.easygoing[3]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr" s="2">
@@ -704,7 +704,7 @@
     <row r="14" ht="40" customHeight="1">
       <c r="A14" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
@@ -719,7 +719,7 @@
       </c>
       <c r="D14" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">badWinner.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">badWinner.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr" s="2">
@@ -736,7 +736,7 @@
     <row r="15" ht="40" customHeight="1">
       <c r="A15" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
@@ -751,7 +751,7 @@
       </c>
       <c r="D15" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodWinner.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">goodWinner.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr" s="2">
@@ -768,7 +768,7 @@
     <row r="16" ht="40" customHeight="1">
       <c r="A16" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">FIRST_MEET_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
@@ -783,7 +783,7 @@
       </c>
       <c r="D16" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr" s="2">
@@ -800,7 +800,7 @@
     <row r="17" ht="40" customHeight="1">
       <c r="A17" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
@@ -815,7 +815,7 @@
       </c>
       <c r="D17" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">loser.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr" s="2">
@@ -832,7 +832,7 @@
     <row r="18" ht="40" customHeight="1">
       <c r="A18" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
@@ -847,7 +847,7 @@
       </c>
       <c r="D18" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">winner.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr" s="2">
@@ -864,7 +864,7 @@
     <row r="19" ht="40" customHeight="1">
       <c r="A19" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
@@ -879,7 +879,7 @@
       </c>
       <c r="D19" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">competition_won.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr" s="2">
@@ -896,7 +896,7 @@
     <row r="20" ht="40" customHeight="1">
       <c r="A20" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
@@ -911,7 +911,7 @@
       </c>
       <c r="D20" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">competition_won.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr" s="2">
@@ -928,7 +928,7 @@
     <row r="21" ht="40" customHeight="1">
       <c r="A21" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.easygoing.delinquent[3]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.delinquent.easygoing[3]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
@@ -943,7 +943,7 @@
       </c>
       <c r="D21" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.easygoing.delinquent[3]</t>
+          <t xml:space="preserve">competition_won.delinquent.easygoing[3]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr" s="2">
@@ -960,7 +960,7 @@
     <row r="22" ht="40" customHeight="1">
       <c r="A22" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
@@ -975,7 +975,7 @@
       </c>
       <c r="D22" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">direct.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr" s="2">
@@ -992,7 +992,7 @@
     <row r="23" ht="40" customHeight="1">
       <c r="A23" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="D23" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">direct.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr" s="2">
@@ -1024,7 +1024,7 @@
     <row r="24" ht="40" customHeight="1">
       <c r="A24" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="D24" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">fa_signing.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr" s="2">
@@ -1056,7 +1056,7 @@
     <row r="25" ht="40" customHeight="1">
       <c r="A25" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="D25" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">fa_signing.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr" s="2">
@@ -1088,7 +1088,7 @@
     <row r="26" ht="40" customHeight="1">
       <c r="A26" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.easygoing.delinquent.hit[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.delinquent.easygoing.hit[1]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="D26" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent.hit[1]</t>
+          <t xml:space="preserve">delinquent.easygoing.hit[1]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr" s="2">
@@ -1120,7 +1120,7 @@
     <row r="27" ht="40" customHeight="1">
       <c r="A27" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.easygoing.delinquent.hit[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.delinquent.easygoing.hit[2]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="D27" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent.hit[2]</t>
+          <t xml:space="preserve">delinquent.easygoing.hit[2]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr" s="2">
@@ -1152,7 +1152,7 @@
     <row r="28" ht="40" customHeight="1">
       <c r="A28" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.easygoing.delinquent.win[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.delinquent.easygoing.win[1]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="D28" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent.win[1]</t>
+          <t xml:space="preserve">delinquent.easygoing.win[1]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr" s="2">
@@ -1184,7 +1184,7 @@
     <row r="29" ht="40" customHeight="1">
       <c r="A29" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.easygoing.delinquent.win[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.delinquent.easygoing.win[2]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="D29" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent.win[2]</t>
+          <t xml:space="preserve">delinquent.easygoing.win[2]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr" s="2">
@@ -1216,7 +1216,7 @@
     <row r="30" ht="40" customHeight="1">
       <c r="A30" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="D30" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr" s="2">
@@ -1248,7 +1248,7 @@
     <row r="31" ht="40" customHeight="1">
       <c r="A31" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="D31" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[2]</t>
+          <t xml:space="preserve">delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr" s="2">
@@ -1280,7 +1280,7 @@
     <row r="32" ht="40" customHeight="1">
       <c r="A32" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.easygoing.delinquent[3]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.delinquent.easygoing[3]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="D32" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[3]</t>
+          <t xml:space="preserve">delinquent.easygoing[3]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr" s="2">
@@ -1312,7 +1312,7 @@
     <row r="33" ht="40" customHeight="1">
       <c r="A33" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="D33" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr" s="2">
@@ -1344,7 +1344,7 @@
     <row r="34" ht="40" customHeight="1">
       <c r="A34" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="D34" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[2]</t>
+          <t xml:space="preserve">delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr" s="2">
@@ -1376,7 +1376,7 @@
     <row r="35" ht="40" customHeight="1">
       <c r="A35" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.easygoing.delinquent[3]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.delinquent.easygoing[3]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="D35" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[3]</t>
+          <t xml:space="preserve">delinquent.easygoing[3]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr" s="2">
@@ -1408,7 +1408,7 @@
     <row r="36" ht="40" customHeight="1">
       <c r="A36" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="D36" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr" s="2">
@@ -1440,7 +1440,7 @@
     <row r="37" ht="40" customHeight="1">
       <c r="A37" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="D37" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[2]</t>
+          <t xml:space="preserve">delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr" s="2">
@@ -1472,7 +1472,7 @@
     <row r="38" ht="40" customHeight="1">
       <c r="A38" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.easygoing.delinquent[3]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.delinquent.easygoing[3]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="D38" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[3]</t>
+          <t xml:space="preserve">delinquent.easygoing[3]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr" s="2">
@@ -1504,7 +1504,7 @@
     <row r="39" ht="40" customHeight="1">
       <c r="A39" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="D39" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr" s="2">
@@ -1536,7 +1536,7 @@
     <row r="40" ht="40" customHeight="1">
       <c r="A40" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="D40" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[2]</t>
+          <t xml:space="preserve">delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr" s="2">
@@ -1568,7 +1568,7 @@
     <row r="41" ht="40" customHeight="1">
       <c r="A41" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.easygoing.delinquent[3]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.delinquent.easygoing[3]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="D41" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[3]</t>
+          <t xml:space="preserve">delinquent.easygoing[3]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr" s="2">
@@ -1600,7 +1600,7 @@
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="D42" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E42" t="inlineStr" s="2">
@@ -1632,7 +1632,7 @@
     <row r="43" ht="40" customHeight="1">
       <c r="A43" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="D43" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[2]</t>
+          <t xml:space="preserve">delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E43" t="inlineStr" s="2">
@@ -1664,7 +1664,7 @@
     <row r="44" ht="40" customHeight="1">
       <c r="A44" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="D44" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr" s="2">
@@ -1696,7 +1696,7 @@
     <row r="45" ht="40" customHeight="1">
       <c r="A45" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="D45" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[2]</t>
+          <t xml:space="preserve">delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E45" t="inlineStr" s="2">
@@ -1728,7 +1728,7 @@
     <row r="46" ht="40" customHeight="1">
       <c r="A46" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="D46" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">loser.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr" s="2">
@@ -1760,7 +1760,7 @@
     <row r="47" ht="40" customHeight="1">
       <c r="A47" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="D47" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">winner.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E47" t="inlineStr" s="2">
@@ -1792,7 +1792,7 @@
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="D48" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">loser.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E48" t="inlineStr" s="2">
@@ -1824,7 +1824,7 @@
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="D49" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">winner.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E49" t="inlineStr" s="2">
@@ -1856,7 +1856,7 @@
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="D50" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">attacker.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr" s="2">
@@ -1888,7 +1888,7 @@
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="D51" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">defender.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr" s="2">
@@ -1920,7 +1920,7 @@
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="D52" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">attacker.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E52" t="inlineStr" s="2">
@@ -1952,7 +1952,7 @@
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">defender.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr" s="2">
@@ -1984,7 +1984,7 @@
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">attacker.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr" s="2">
@@ -2016,7 +2016,7 @@
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">defender.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr" s="2">
@@ -2048,7 +2048,7 @@
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">loserLines.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr" s="2">
@@ -2080,7 +2080,7 @@
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">winnerLines.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr" s="2">
@@ -2112,7 +2112,7 @@
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">loser.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr" s="2">
@@ -2144,7 +2144,7 @@
     <row r="59" ht="40" customHeight="1">
       <c r="A59" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="D59" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">winner.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E59" t="inlineStr" s="2">
@@ -2176,7 +2176,7 @@
     <row r="60" ht="40" customHeight="1">
       <c r="A60" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="D60" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">loserLines.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E60" t="inlineStr" s="2">
@@ -2208,7 +2208,7 @@
     <row r="61" ht="40" customHeight="1">
       <c r="A61" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="D61" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">winnerLines.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E61" t="inlineStr" s="2">
@@ -2240,7 +2240,7 @@
     <row r="62" ht="40" customHeight="1">
       <c r="A62" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="D62" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">awakening.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">awakening.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E62" t="inlineStr" s="2">
@@ -3040,7 +3040,7 @@
     <row r="87" ht="40" customHeight="1">
       <c r="A87" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="D87" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">accepted.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr" s="2">
@@ -3072,7 +3072,7 @@
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">defended.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr" s="2">
@@ -3104,7 +3104,7 @@
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">defense_failed.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr" s="2">
@@ -3136,7 +3136,7 @@
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.default.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.default.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">default.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">default.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr" s="2">
@@ -3168,7 +3168,7 @@
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">former_champ.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr" s="2">
@@ -3200,7 +3200,7 @@
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.heel.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.heel.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heel.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">heel.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr" s="2">
@@ -3232,7 +3232,7 @@
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.high_trust.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.high_trust.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">high_trust.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">high_trust.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr" s="2">
@@ -3264,7 +3264,7 @@
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_former_champ.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">accept_former_champ.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr" s="2">
@@ -3296,7 +3296,7 @@
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_heel.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">accept_heel.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr" s="2">
@@ -3328,7 +3328,7 @@
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_no_title.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">accept_no_title.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
@@ -3360,7 +3360,7 @@
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3375,7 +3375,7 @@
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">accept_terminal.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
@@ -3392,7 +3392,7 @@
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_winless.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">accept_winless.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
@@ -3424,7 +3424,7 @@
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">refuse_champ.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
@@ -3456,7 +3456,7 @@
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_distrust.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">refuse_distrust.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
@@ -3488,7 +3488,7 @@
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_fighting.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">refuse_fighting.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
@@ -3520,7 +3520,7 @@
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_heel.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">refuse_heel.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
@@ -3552,7 +3552,7 @@
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">A1_champion.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
@@ -3584,7 +3584,7 @@
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">A2_uncrowned.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
@@ -3616,7 +3616,7 @@
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">A3_heel.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
@@ -3648,7 +3648,7 @@
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">A4_veteran.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
@@ -3680,7 +3680,7 @@
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">B1_young.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
@@ -3712,7 +3712,7 @@
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">B2_prime.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
@@ -3744,7 +3744,7 @@
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">B3_older.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
@@ -3776,7 +3776,7 @@
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">B4_champion_injury.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
@@ -3808,7 +3808,7 @@
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
@@ -3840,7 +3840,7 @@
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">raise_accept.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -3872,7 +3872,7 @@
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -3904,7 +3904,7 @@
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -3936,7 +3936,7 @@
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">raise_open.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -3968,7 +3968,7 @@
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">raise_refuse.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -4000,7 +4000,7 @@
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">sudden_departure.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4025,14 +4025,14 @@
       </c>
       <c r="F117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">聞いてくれんの？ {record}なんつーか、マンネリなんだよな。新しいとこ行きてーんだ。</t>
+          <t xml:space="preserve">いやー、ついにこの日が来ちまったっすね。じゃ、元気で。</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">sudden_departure.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -4057,14 +4057,14 @@
       </c>
       <c r="F118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。{tenure}悪いけどさー、ちょっと外に出てみたいんだよね。</t>
+          <t xml:space="preserve">もう潮時っしょ。楽しかったっすよ、うん。じゃあ、失礼します。</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4079,7 +4079,7 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">transfer_listen.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -4089,14 +4089,14 @@
       </c>
       <c r="F119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まーそうなるよなー。{tenure_farewell}{rivalry}元気でな！</t>
+          <t xml:space="preserve">聞いてくれんの？ {record}なんつーか、マンネリなんだよな。新しいとこ行きてーんだ。</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">transfer_open.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
@@ -4121,14 +4121,14 @@
       </c>
       <c r="F120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悪いな社長。金の問題じゃねーんだよ。もう決めちまったから。</t>
+          <t xml:space="preserve">社長。{tenure}悪いけどさー、ちょっと外に出てみたいんだよね。</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">transfer_release.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
@@ -4153,14 +4153,14 @@
       </c>
       <c r="F121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マジかよ。そこまでしてくれんの？ じゃーもうちょいいるか！</t>
+          <t xml:space="preserve">まーそうなるよなー。{tenure_farewell}{rivalry}元気でな！</t>
         </is>
       </c>
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.blocked.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4170,193 +4170,193 @@
       </c>
       <c r="C122" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_fail.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">悪いな社長。金の問題じゃねーんだよ。もう決めちまったから。</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="40" customHeight="1">
+      <c r="A123" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_success.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">マジかよ。そこまでしてくれんの？ じゃーもうちょいいるか！</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="40" customHeight="1">
+      <c r="A124" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">NEGOTIATE_LINES.blocked.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">blocked.easygoing.delinquent[1]</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr" s="2">
+      <c r="D124" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">blocked.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr" s="3">
+      <c r="F124" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">おっ、引き抜きか！気持ちは嬉しいけどな、
 今の仲間が好きすぎて動けないわ！</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="40" customHeight="1">
-      <c r="A123" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.fail.easygoing.delinquent[1]</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr" s="2">
+    <row r="125" ht="40" customHeight="1">
+      <c r="A125" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">NEGOTIATE_LINES.fail.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">fail.easygoing.delinquent[1]</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr" s="2">
+      <c r="D125" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fail.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr" s="3">
+      <c r="F125" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">ごめんな〜、今のとこが好きなんだよ！
 またな！</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="40" customHeight="1">
-      <c r="A124" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.easygoing.delinquent[1]</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr" s="2">
+    <row r="126" ht="40" customHeight="1">
+      <c r="A126" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">start.easygoing.delinquent[1]</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr" s="2">
+      <c r="D126" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">start.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr" s="3">
+      <c r="F126" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">マジで！？ スカウト！？
 話聞かせてくれよ！</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="40" customHeight="1">
-      <c r="A125" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.success.easygoing.delinquent[1]</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr" s="2">
+    <row r="127" ht="40" customHeight="1">
+      <c r="A127" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">NEGOTIATE_LINES.success.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">success.easygoing.delinquent[1]</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr" s="2">
+      <c r="D127" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">success.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr" s="3">
+      <c r="F127" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">やったぜ！ 新しい団体！
 楽しみすぎて眠れねーよ！</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="40" customHeight="1">
-      <c r="A126" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.easygoing.delinquent[1]</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">おお！ なんかいつもと違うぜ！ いい感じ！</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="40" customHeight="1">
-      <c r="A127" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.easygoing.delinquent[1]</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">fresh.easygoing.delinquent[1]</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">お、今日は体が軽ぃな。もう一本いこうぜ</t>
-        </is>
-      </c>
-    </row>
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4366,29 +4366,29 @@
       </c>
       <c r="C128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heavy.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体がだりぃわ。今日やっても、ザルに水だろ</t>
+          <t xml:space="preserve">社長〜、あたしらの子のこと、たまには可愛がってやってくれません?</t>
         </is>
       </c>
     </row>
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4398,29 +4398,29 @@
       </c>
       <c r="C129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warm.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんか今日、乗んねーな。ま、動けてるからいっか</t>
+          <t xml:space="preserve">社長〜、次のメイン、あたしらで暴れさせてくれません?</t>
         </is>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4430,29 +4430,29 @@
       </c>
       <c r="C130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあいいや、ここまで来れただけでも上等だぜ</t>
+          <t xml:space="preserve">社長〜、お給料の件、ちょっと色つけてくんないっすかね〜?</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4462,29 +4462,29 @@
       </c>
       <c r="C131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マジか、ここまで来ちゃったぜ！</t>
+          <t xml:space="preserve">社長〜、あたしらの頑張り、たまには口に出してくれませんかね〜?</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4494,29 +4494,29 @@
       </c>
       <c r="C132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おー、いい感じに仕上がってきたぜ</t>
+          <t xml:space="preserve">マジっすか、社長ありがとう〜! 嬉しいっすね。</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4526,29 +4526,29 @@
       </c>
       <c r="C133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うっひょー！ 最強じゃね？</t>
+          <t xml:space="preserve">あ、はい〜。まあ社長忙しいっすもんね。</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4558,29 +4558,29 @@
       </c>
       <c r="C134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高だぜ！ もっと声出せ〜！</t>
+          <t xml:space="preserve">へぇ、別ルートっすか〜。まあ気持ちは受け取ります〜。</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4590,29 +4590,29 @@
       </c>
       <c r="C135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんだろうな…楽しいって感覚、どこ行っちまったんだ</t>
+          <t xml:space="preserve">マジですか? 社長ありがとう! 暴れさせてもらいますね〜!</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4622,29 +4622,29 @@
       </c>
       <c r="C136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おっし、やる気出てきたぜ！ 楽しまねーとな</t>
+          <t xml:space="preserve">えぇ〜、つれないっすね〜。まあいいっすけど。</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4654,29 +4654,29 @@
       </c>
       <c r="C137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いやー長かったな！ でもまた楽しくなってきたぜ</t>
+          <t xml:space="preserve">へぇ、そっちっすか? まあ、ありがたいっすけど〜。</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4686,29 +4686,29 @@
       </c>
       <c r="C138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんだろうな…いつもみたいに動かねーよ</t>
+          <t xml:space="preserve">マジで上げてくれんすか?! 社長太っ腹〜! みんなにも言っときます!</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4718,29 +4718,29 @@
       </c>
       <c r="C139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あれ、治ったはずなのに調子でねーな</t>
+          <t xml:space="preserve">えぇ〜、ケチっすね〜。まあ次に期待してますんで〜。</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4750,29 +4750,29 @@
       </c>
       <c r="C140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まいったな…リングがちょっと怖ぇーよ</t>
+          <t xml:space="preserve">へぇ、お金じゃないんすか〜。まあ気持ちは嬉しいっす〜。</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4782,29 +4782,29 @@
       </c>
       <c r="C141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">怪我は治ったんだけどな…なんか乗んねーわ</t>
+          <t xml:space="preserve">マジっすか〜、社長に褒められちゃった〜! ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4814,29 +4814,29 @@
       </c>
       <c r="C142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">終わった瞬間「もう1ラウンドくれ！」って叫びそうになった！</t>
+          <t xml:space="preserve">えぇ〜、つれないっすね〜。まあいいっすけど〜。</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4846,29 +4846,29 @@
       </c>
       <c r="C143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンの響き、たまんねえ！ もっと楽しむぜ！</t>
+          <t xml:space="preserve">へぇ、別ルートっすか〜。まあ気持ちは受け取ります〜。</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4878,29 +4878,29 @@
       </c>
       <c r="C144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最っ高に楽しい選手人生だったぜ！ みんなありがとな！ プロレス最高！</t>
+          <t xml:space="preserve">え、気にしてました? ごめんなさ〜い、次は誘いますんで〜。</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4910,29 +4910,29 @@
       </c>
       <c r="C145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うおお！ MVP！ いい響きじゃん！</t>
+          <t xml:space="preserve">ありがとうござ〜っす、楽しんできまっす。</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4942,29 +4942,29 @@
       </c>
       <c r="C146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うっそだろ！？ まあいいや、もらえるもんはもらっとく！</t>
+          <t xml:space="preserve">あ、そっかぁ〜、気をつけまっす。</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -4974,29 +4974,29 @@
       </c>
       <c r="C147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おーっ、ドームか。まぁやるだけよ</t>
+          <t xml:space="preserve">ありがとうござ〜っす。</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5006,29 +5006,29 @@
       </c>
       <c r="C148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[2]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんつーか、あんま緊張しねーな。やるべ</t>
+          <t xml:space="preserve">えぇ〜、客ノッてたじゃないっすか〜。はい、控えまっす。</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.easygoing.delinquent[3]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5038,29 +5038,29 @@
       </c>
       <c r="C149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[3]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いつも通りだろ。気楽に行こうぜ</t>
+          <t xml:space="preserve">やった〜、社長わかってる〜! 引き続き暴れまっす!</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5070,29 +5070,29 @@
       </c>
       <c r="C150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マジで満員かよ! やっべ、嬉しくて笑えてきたわ</t>
+          <t xml:space="preserve">あ〜ばれてました? すんませ〜ん、明日から出まっす。</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5102,29 +5102,29 @@
       </c>
       <c r="C151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[2]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">観客全員ぶち上がってたな! 気持ち良かったぜ</t>
+          <t xml:space="preserve">マジっすか〜、社長太っ腹! 助かります〜。</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.easygoing.delinquent[3]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5134,29 +5134,29 @@
       </c>
       <c r="C152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[3]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こういう日もあんだな、人生ってよ</t>
+          <t xml:space="preserve">へぇ、メンバーケアっすか〜。まあありがたいっす。</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5166,29 +5166,29 @@
       </c>
       <c r="C153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんか急にキタわ！掴めた感じ！</t>
+          <t xml:space="preserve">えへ、バレてました〜? じゃお言葉に甘えて休みまっす。</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5198,29 +5198,29 @@
       </c>
       <c r="C154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あいつ最高！一緒だとテンション上がるわ！</t>
+          <t xml:space="preserve">いやいや、まだいけますって〜。</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5230,29 +5230,29 @@
       </c>
       <c r="C155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あー疲れた。ちょい休むわ</t>
+          <t xml:space="preserve">へぇ、メンバー優先っすか〜。助かりますね〜。</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5262,29 +5262,29 @@
       </c>
       <c r="C156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンが盛り上がってんの最高じゃん！</t>
+          <t xml:space="preserve">えー、そんな話してました? まあ注意しときますんで〜。</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5294,29 +5294,29 @@
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もーいいわ。考えさせてくれ</t>
+          <t xml:space="preserve">お〜、放っといてくれるんすか〜。ありがたいっす〜。</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5326,29 +5326,29 @@
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あー…いや、なんでもねー。平気平気</t>
+          <t xml:space="preserve">へぇ、別ルートっすか。下の子のケア助かります〜。</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5358,29 +5358,29 @@
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やった！ラッキー！</t>
+          <t xml:space="preserve">あー、はい〜、気をつけまーす。</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5390,29 +5390,29 @@
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">合宿だー！ 盛り上がっていくぞー！</t>
+          <t xml:space="preserve">（へらっと笑って、誤魔化した）</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5422,29 +5422,29 @@
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見てくれてたんだ？ じゃ、もうちょいやるか！</t>
+          <t xml:space="preserve">へぇ、別ルートっすか〜。まあ気持ちは受け取ります〜。</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5454,29 +5454,29 @@
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おっしゃ！元気出た！やってやるわ！</t>
+          <t xml:space="preserve">えぇ〜、これくらいいけるんすけどな〜。はい、緩めまっす。</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5486,29 +5486,29 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えー。せっかく楽しくやってたのに</t>
+          <t xml:space="preserve">お〜、続けていいんすか〜! やった〜!</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5518,29 +5518,29 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テレビ！？ みんな見てるー？</t>
+          <t xml:space="preserve">あれ、あたしじゃなくて子たち優先っすか〜? まあありがたいっす。</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.easygoing.attack.delinquent</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5550,29 +5550,29 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">easygoing.attack.delinquent</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うぇーい！飲むぞ〜！</t>
+          <t xml:space="preserve">仲良しごっこは終わりだな</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.easygoing.defend.delinquent</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5582,29 +5582,29 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">easygoing.defend.delinquent</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">バカンスだー！戻ったら本気出すから！</t>
+          <t xml:space="preserve">ま、しゃあねえな</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5614,29 +5614,29 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マジか！すぐ治してくる！</t>
+          <t xml:space="preserve">おお！ なんかいつもと違うぜ！ いい感じ！</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5646,29 +5646,29 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">fresh.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マンツーマン！？ 超贅沢じゃん！</t>
+          <t xml:space="preserve">お、今日は体が軽ぃな。もう一本いこうぜ</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5678,29 +5678,29 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">heavy.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テレビ出んの！？ 最高じゃん！</t>
+          <t xml:space="preserve">体がだりぃわ。今日やっても、ザルに水だろ</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5710,29 +5710,29 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">warm.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">他所から話来たんだけど！ちょっと嬉しくね？</t>
+          <t xml:space="preserve">なんか今日、乗んねーな。ま、動けてるからいっか</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5742,29 +5742,29 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">cap_reached.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はは…今日はサボるわ…</t>
+          <t xml:space="preserve">まあいいや、ここまで来れただけでも上等だぜ</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5774,29 +5774,29 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">ovr_elite.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習な…うーん、今日はパスで</t>
+          <t xml:space="preserve">マジか、ここまで来ちゃったぜ！</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5806,29 +5806,29 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">ovr_growth.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（いつもの軽口が消え、「なぁ、ちょっとさぁ…」と珍しく愚痴をこぼしている）</t>
+          <t xml:space="preserve">おー、いい感じに仕上がってきたぜ</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5838,29 +5838,29 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">ovr_legend.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに「最近ちょい考えることあってさ」と珍しく真面目な投稿）</t>
+          <t xml:space="preserve">うっひょー！ 最強じゃね？</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5870,29 +5870,29 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">pop_star.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">タイトルマッチ組めよ！やる気あんだからさ！</t>
+          <t xml:space="preserve">最高だぜ！ もっと声出せ〜！</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5902,29 +5902,29 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あいつとやらせろよ！ケリつけてやる！</t>
+          <t xml:space="preserve">なんだろうな…楽しいって感覚、どこ行っちまったんだ</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5934,29 +5934,29 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">無理！限界！休ませて！</t>
+          <t xml:space="preserve">おっし、やる気出てきたぜ！ 楽しまねーとな</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5966,29 +5966,29 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう無理！ちゃんと話し合えよ！</t>
+          <t xml:space="preserve">いやー長かったな！ でもまた楽しくなってきたぜ</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -5998,29 +5998,29 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">defeat.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あー…いや、なんでもねえって（笑ってはいるが、目が笑っていない）</t>
+          <t xml:space="preserve">なんだろうな…いつもみたいに動かねーよ</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6030,29 +6030,29 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">特訓すんぞ！もっと強くなりてーんだよ！</t>
+          <t xml:space="preserve">あれ、治ったはずなのに調子でねーな</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6062,29 +6062,29 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">後輩の面倒見るわ！任せとけ！</t>
+          <t xml:space="preserve">まいったな…リングがちょっと怖ぇーよ</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6094,29 +6094,29 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">penalty_end.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いった！やっちまったけど、すぐ治すから！</t>
+          <t xml:space="preserve">怪我は治ったんだけどな…なんか乗んねーわ</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6126,29 +6126,29 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">bestMatch.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あいつマジ無理！もう顔も見たくねえ！</t>
+          <t xml:space="preserve">終わった瞬間「もう1ラウンドくれ！」って叫びそうになった！</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6158,29 +6158,29 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">champion.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やんのか！？ 売られたケンカは買うぜ！</t>
+          <t xml:space="preserve">チャンピオンの響き、たまんねえ！ もっと楽しむぜ！</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6190,29 +6190,29 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">hallOfFame.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">コラボか。なんか面白そうじゃん</t>
+          <t xml:space="preserve">最っ高に楽しい選手人生だったぜ！ みんなありがとな！ プロレス最高！</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6222,29 +6222,29 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">mvp.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">CM撮影！？ 楽しそうじゃん！</t>
+          <t xml:space="preserve">うおお！ MVP！ いい響きじゃん！</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6254,29 +6254,29 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">rookie.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンと直接会えるのいいじゃん！ 楽しみ！</t>
+          <t xml:space="preserve">うっそだろ！？ まあいいや、もらえるもんはもらっとく！</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6286,29 +6286,29 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ランウェイか。めっちゃ目立てそうじゃん！</t>
+          <t xml:space="preserve">おーっ、ドームか。まぁやるだけよ</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6318,29 +6318,29 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">グラビアか。まぁ、派手にやってやる</t>
+          <t xml:space="preserve">なんつーか、あんま緊張しねーな。やるべ</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.delinquent.easygoing[3]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6350,29 +6350,29 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[3]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テレビで暴れてやる！ 楽しみ！</t>
+          <t xml:space="preserve">いつも通りだろ。気楽に行こうぜ</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6382,29 +6382,29 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テレビ！？ マジ！？ やったー！</t>
+          <t xml:space="preserve">マジで満員かよ! やっべ、嬉しくて笑えてきたわ</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6414,29 +6414,29 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しくやろうぜ！退屈なのは嫌いだからな！</t>
+          <t xml:space="preserve">観客全員ぶち上がってたな! 気持ち良かったぜ</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.delinquent.easygoing[3]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6446,29 +6446,29 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[3]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よっ、よろしくな! 楽しくやろうぜ</t>
+          <t xml:space="preserve">こういう日もあんだな、人生ってよ</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6478,29 +6478,29 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">N1.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よっしゃー！新天地だ！暴れるぞ！</t>
+          <t xml:space="preserve">なんか急にキタわ！掴めた感じ！</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6510,29 +6510,29 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">N2.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よっしゃー！楽しくやろうぜ！</t>
+          <t xml:space="preserve">あいつ最高！一緒だとテンション上がるわ！</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6542,29 +6542,29 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">N3.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やっちまったぜ〜 まぁすぐ戻るわ</t>
+          <t xml:space="preserve">あー疲れた。ちょい休むわ</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6574,29 +6574,29 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">N4.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しくやろうぜ！退屈なのは嫌いだからな！</t>
+          <t xml:space="preserve">ファンが盛り上がってんの最高じゃん！</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6606,29 +6606,29 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">N5_low.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よっ、よろしくな! 楽しくやろうぜ</t>
+          <t xml:space="preserve">もーいいわ。考えさせてくれ</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6638,29 +6638,29 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">N5_warning.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">フリーもそろそろ飽きたんでな。世話になるぜ</t>
+          <t xml:space="preserve">あー…いや、なんでもねー。平気平気</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6670,29 +6670,29 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">bonus.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よっしゃー！新天地だ！暴れるぞ！</t>
+          <t xml:space="preserve">やった！ラッキー！</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6702,29 +6702,29 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">camp.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よっしゃー！楽しくやろうぜ！</t>
+          <t xml:space="preserve">合宿だー！ 盛り上がっていくぞー！</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6734,29 +6734,29 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">encourage_high_trust.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お、今日は体が軽ぃな。もう一本いこうぜ</t>
+          <t xml:space="preserve">見てくれてたんだ？ じゃ、もうちょいやるか！</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6766,29 +6766,29 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">encourage.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体がだりぃわ。今日やっても、ザルに水だろ</t>
+          <t xml:space="preserve">おっしゃ！元気出た！やってやるわ！</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6798,29 +6798,29 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">faction_decree.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんか今日、乗んねーな。ま、動けてるからいっか</t>
+          <t xml:space="preserve">えー。せっかく楽しくやってたのに</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6830,29 +6830,29 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">media.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やっちまったぜ〜 まぁすぐ戻るわ</t>
+          <t xml:space="preserve">テレビ！？ みんな見てるー？</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6862,29 +6862,29 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">party.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ、こんなもんか。元気でやれよ〜</t>
+          <t xml:space="preserve">うぇーい！飲むぞ〜！</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6894,29 +6894,29 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">refresh_leave.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おじゃまー！暴れさせてもらうぜ！</t>
+          <t xml:space="preserve">バカンスだー！戻ったら本気出すから！</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6926,29 +6926,29 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">special_treatment.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">スカウトってのも、けっこう悪い気しねーな。やる気出てきたっ！</t>
+          <t xml:space="preserve">マジか！すぐ治してくる！</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6958,29 +6958,29 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">trainer.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそー！悔しい！でも次やってやるからな！</t>
+          <t xml:space="preserve">マンツーマン！？ 超贅沢じゃん！</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -6990,29 +6990,29 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">E1.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだまだ渡さねーよ！最高！</t>
+          <t xml:space="preserve">テレビ出んの！？ 最高じゃん！</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7022,29 +7022,29 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">E6.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそー！でもまだ終わってねえから！</t>
+          <t xml:space="preserve">他所から話来たんだけど！ちょっと嬉しくね？</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7054,29 +7054,29 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">S_boycott.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンだぜー！最高だろ！</t>
+          <t xml:space="preserve">はは…今日はサボるわ…</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7086,29 +7086,29 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">S_boycott.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ、こんなもんか。元気でやれよ〜</t>
+          <t xml:space="preserve">練習な…うーん、今日はパスで</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7118,29 +7118,29 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">S_grumble.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おじゃまー！暴れさせてもらうぜ！</t>
+          <t xml:space="preserve">（いつもの軽口が消え、「なぁ、ちょっとさぁ…」と珍しく愚痴をこぼしている）</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7150,29 +7150,29 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">S_sns.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそー！悔しい！でも次やってやるからな！</t>
+          <t xml:space="preserve">（SNSに「最近ちょい考えることあってさ」と珍しく真面目な投稿）</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7182,29 +7182,29 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">S1.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだまだ渡さねーよ！最高！</t>
+          <t xml:space="preserve">タイトルマッチ組めよ！やる気あんだからさ！</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7214,29 +7214,29 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">S2.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそー！でもまだ終わってねえから！</t>
+          <t xml:space="preserve">あいつとやらせろよ！ケリつけてやる！</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7246,29 +7246,29 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">S3.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンだぜー！最高だろ！</t>
+          <t xml:space="preserve">無理！限界！休ませて！</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7278,29 +7278,29 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">S4_direct.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う〜ん、ちょい合わねぇかもな…</t>
+          <t xml:space="preserve">もう無理！ちゃんと話し合えよ！</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7310,29 +7310,29 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">S4_silent.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あれ〜、最近ちょい素っ気なくね？</t>
+          <t xml:space="preserve">あー…いや、なんでもねえって（笑ってはいるが、目が笑っていない）</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7342,29 +7342,29 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">S5.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">んー、なんか空気変わった気ぃすんだけど</t>
+          <t xml:space="preserve">特訓すんぞ！もっと強くなりてーんだよ！</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7374,29 +7374,29 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">S6.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">つるんでると楽しいんだわ、まじで</t>
+          <t xml:space="preserve">後輩の面倒見るわ！任せとけ！</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7406,29 +7406,29 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">B1.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一生の仲間だぜ。間違いない</t>
+          <t xml:space="preserve">いった！やっちまったけど、すぐ治すから！</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7438,29 +7438,29 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">B2_fighter1.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">熱い関係も一段落かぁ。ちっと寂しいな</t>
+          <t xml:space="preserve">あいつマジ無理！もう顔も見たくねえ！</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7470,29 +7470,29 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">B2_fighter2.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ因縁も永遠じゃねぇよな〜</t>
+          <t xml:space="preserve">やんのか！？ 売られたケンカは買うぜ！</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7502,29 +7502,29 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">B4_brand.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やり合うの、ワクワクすんだよな</t>
+          <t xml:space="preserve">コラボか。なんか面白そうじゃん</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7534,29 +7534,29 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">B4_cm.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">本気でやり合いてぇ相手なんて、そうはいねぇよ</t>
+          <t xml:space="preserve">CM撮影！？ 楽しそうじゃん！</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7566,29 +7566,29 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">B4_fan.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">へへ、考えると自然に気合入るんだわ</t>
+          <t xml:space="preserve">ファンと直接会えるのいいじゃん！ 楽しみ！</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7598,29 +7598,29 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">B4_fashion.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この試合が一番楽しいんだわ。ずっと続けばいいのにな</t>
+          <t xml:space="preserve">ランウェイか。めっちゃ目立てそうじゃん！</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7630,29 +7630,29 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">B4_gravure.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">運命のライバルってやつだろ。最高だぜ</t>
+          <t xml:space="preserve">グラビアか。まぁ、派手にやってやる</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7662,29 +7662,29 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">B4_variety.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここ最高〜！ みんなとやんの楽しいわ！</t>
+          <t xml:space="preserve">テレビで暴れてやる！ 楽しみ！</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7694,29 +7694,29 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">B4.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体、すげぇ居心地いいんだわ〜</t>
+          <t xml:space="preserve">テレビ！？ マジ！？ やったー！</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7726,29 +7726,29 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">さすがにこれは…笑えねぇかも</t>
+          <t xml:space="preserve">楽しくやろうぜ！退屈なのは嫌いだからな！</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7758,29 +7758,29 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あはは…って笑ってる場合じゃねぇよな、これ</t>
+          <t xml:space="preserve">よっ、よろしくな! 楽しくやろうぜ</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7790,29 +7790,29 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う〜ん、最近ちっとモヤモヤすんだよなぁ…</t>
+          <t xml:space="preserve">よっしゃー！新天地だ！暴れるぞ！</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7822,29 +7822,29 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ大丈夫…だよな？ ちょい不安だけど</t>
+          <t xml:space="preserve">よっしゃー！楽しくやろうぜ！</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7854,29 +7854,29 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">終わっちまったかー。まぁ次また来るっしょ</t>
+          <t xml:space="preserve">やっちまったぜ〜 まぁすぐ戻るわ</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7886,29 +7886,29 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">draftInterest.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いやー身体ガタガタだわ。でも最後だし、暴れて終わろうぜ</t>
+          <t xml:space="preserve">楽しくやろうぜ！退屈なのは嫌いだからな！</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7918,29 +7918,29 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">draftJoin.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで残っちまったな。ま、痛いのは後で考えるわ</t>
+          <t xml:space="preserve">よっ、よろしくな! 楽しくやろうぜ</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7950,29 +7950,29 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">faGreeting.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手は誰だ? ま、来た奴から順にぶっ倒すだけだ</t>
+          <t xml:space="preserve">フリーもそろそろ飽きたんでな。世話になるぜ</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -7982,29 +7982,29 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">faSigning.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いいぜいいぜ、次々来いよ。まとめて相手してやるって</t>
+          <t xml:space="preserve">よっしゃー！新天地だ！暴れるぞ！</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8014,29 +8014,29 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">faWelcome.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人ぶっ倒したー! …はぁ、まだいけるっしょ。次、出てこいよー</t>
+          <t xml:space="preserve">よっしゃー！楽しくやろうぜ！</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8046,29 +8046,29 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">heatSelf.fresh.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふう、一丁上がり。でもまだ終わってねえぞ。次、さっさと来い</t>
+          <t xml:space="preserve">お、今日は体が軽ぃな。もう一本いこうぜ</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8078,29 +8078,29 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">heatSelf.heavy.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で勝ったぜ！ いやー、最高の気分だな</t>
+          <t xml:space="preserve">体がだりぃわ。今日やっても、ザルに水だろ</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8110,29 +8110,29 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">heatSelf.warm.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間がいたから全然余裕だったっての。まあ、ちょっとは焦ったけどな</t>
+          <t xml:space="preserve">なんか今日、乗んねーな。ま、動けてるからいっか</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8142,29 +8142,29 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">injury.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVPねえ。まあもらっとくけどさ、一人じゃ盛り上がんねえよ</t>
+          <t xml:space="preserve">やっちまったぜ〜 まぁすぐ戻るわ</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8174,29 +8174,29 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">release.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次は全員で暴れて、全員で勝つ。そうじゃなきゃつまんねえ</t>
+          <t xml:space="preserve">まぁ、こんなもんか。元気でやれよ〜</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8206,29 +8206,29 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">rentalGreeting.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いやー次から次に来んのな。途中から面白くなっちゃったよ</t>
+          <t xml:space="preserve">おじゃまー！暴れさせてもらうぜ！</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8238,29 +8238,29 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">scoutGreeting.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人だっけ？ まあいいや、全員倒したし。あたしの勝ちってことで</t>
+          <t xml:space="preserve">スカウトってのも、けっこう悪い気しねーな。やる気出てきたっ！</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8270,29 +8270,29 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いえ〜い！ 優勝〜！ 最高じゃん！</t>
+          <t xml:space="preserve">くそー！悔しい！でも次やってやるからな！</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8302,29 +8302,29 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">titleDefense.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ひゃっほ〜！ やったぜ〜！</t>
+          <t xml:space="preserve">まだまだ渡さねーよ！最高！</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8334,29 +8334,29 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">titleLoss.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マジかー、負けたわ。ま、次があるし</t>
+          <t xml:space="preserve">くそー！でもまだ終わってねえから！</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8366,29 +8366,29 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">titleWin.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">しゃーねえな。次だ次</t>
+          <t xml:space="preserve">チャンピオンだぜー！最高だろ！</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8398,29 +8398,29 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いえーい！ 楽勝楽勝〜</t>
+          <t xml:space="preserve">まぁ、こんなもんか。元気でやれよ〜</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8430,29 +8430,29 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ノリノリだぜ！ 次も行くぞ〜</t>
+          <t xml:space="preserve">おじゃまー！暴れさせてもらうぜ！</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8462,29 +8462,29 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しかったぜ〜。またやりてえな</t>
+          <t xml:space="preserve">くそー！悔しい！でも次やってやるからな！</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8494,29 +8494,29 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあまあ良かったんじゃね？</t>
+          <t xml:space="preserve">まだまだ渡さねーよ！最高！</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8526,29 +8526,29 @@
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うっひょ〜決勝じゃん！ やるっきゃねえ！</t>
+          <t xml:space="preserve">くそー！でもまだ終わってねえから！</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8558,29 +8558,29 @@
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最後だし、全力で暴れるぜ！</t>
+          <t xml:space="preserve">チャンピオンだぜー！最高だろ！</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8590,29 +8590,29 @@
       </c>
       <c r="C260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">bond_39_down.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よーし、パパッとやっちまうか</t>
+          <t xml:space="preserve">う〜ん、ちょい合わねぇかもな…</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8622,29 +8622,29 @@
       </c>
       <c r="C261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">bond_59_down.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">気楽にいこうぜ。でも手は抜かねえけど</t>
+          <t xml:space="preserve">あれ〜、最近ちょい素っ気なくね？</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8654,29 +8654,29 @@
       </c>
       <c r="C262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">bond_59_down.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マジ？ ウケる。まあ出てやるよ</t>
+          <t xml:space="preserve">んー、なんか空気変わった気ぃすんだけど</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8686,29 +8686,29 @@
       </c>
       <c r="C263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">bond_60_up.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、暴れる場所があるなら出るっしょ</t>
+          <t xml:space="preserve">つるんでると楽しいんだわ、まじで</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8718,29 +8718,29 @@
       </c>
       <c r="C264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">bond_80_up.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高だぜ！楽しもうや！</t>
+          <t xml:space="preserve">一生の仲間だぜ。間違いない</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8750,29 +8750,29 @@
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[2]</t>
+          <t xml:space="preserve">rivalry_29_down.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">へぇ、派手な舞台じゃん！せっかくだし楽しもっかな！</t>
+          <t xml:space="preserve">熱い関係も一段落かぁ。ちっと寂しいな</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8782,29 +8782,29 @@
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">rivalry_29_down.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マジかよ……！ やべえ、勝っちまった……！ 最高だ！</t>
+          <t xml:space="preserve">まぁ因縁も永遠じゃねぇよな〜</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8814,29 +8814,29 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">rivalry_30_up.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よう、暇だから殴りに来たぜ</t>
+          <t xml:space="preserve">やり合うの、ワクワクすんだよな</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8846,29 +8846,29 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[2]</t>
+          <t xml:space="preserve">rivalry_50_up.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">面白えことしようぜ。対抗戦だ対抗戦</t>
+          <t xml:space="preserve">本気でやり合いてぇ相手なんて、そうはいねぇよ</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8878,29 +8878,29 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">rivalry_50_up.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">は？ 逃げんの？ ダッセー</t>
+          <t xml:space="preserve">へへ、考えると自然に気合入るんだわ</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8910,29 +8910,29 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[2]</t>
+          <t xml:space="preserve">rivalry_70_up.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、ビビるのもわかるけどな。またな</t>
+          <t xml:space="preserve">この試合が一番楽しいんだわ。ずっと続けばいいのにな</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8942,29 +8942,29 @@
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">rivalry_70_up.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、こういう日もあるっしょ。次だ次！</t>
+          <t xml:space="preserve">運命のライバルってやつだろ。最高だぜ</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -8974,29 +8974,29 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">trust_above_75.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くっそー、やられた。次は倍返しだ</t>
+          <t xml:space="preserve">ここ最高〜！ みんなとやんの楽しいわ！</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9006,29 +9006,29 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">trust_above_75.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いえーい！ 圧勝だぜ〜！</t>
+          <t xml:space="preserve">この団体、すげぇ居心地いいんだわ〜</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9038,29 +9038,29 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">trust_below_20.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">面白かったぜ！ またかかって来いよ</t>
+          <t xml:space="preserve">さすがにこれは…笑えねぇかも</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9070,29 +9070,29 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">trust_below_20.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よっしゃあ！ 勝った勝った！ 打ち上げだ打ち上げ！</t>
+          <t xml:space="preserve">あはは…って笑ってる場合じゃねぇよな、これ</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9102,29 +9102,29 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[2]</t>
+          <t xml:space="preserve">trust_below_35.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よっしゃ〜！ まだまだいけるぜ〜！</t>
+          <t xml:space="preserve">う〜ん、最近ちっとモヤモヤすんだよなぁ…</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.easygoing.delinquent[3]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9134,29 +9134,29 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[3]</t>
+          <t xml:space="preserve">trust_below_35.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いえーい！ 圧勝〜！ 打ち上げ行くぞ〜！</t>
+          <t xml:space="preserve">まぁ大丈夫…だよな？ ちょい不安だけど</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9166,29 +9166,29 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高だぜ！みんなありがとな！</t>
+          <t xml:space="preserve">終わっちまったかー。まぁ次また来るっしょ</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9198,29 +9198,29 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
+          <t xml:space="preserve">preFinal.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">フリーもそろそろ飽きたんでな。世話になるぜ</t>
+          <t xml:space="preserve">いやー身体ガタガタだわ。でも最後だし、暴れて終わろうぜ</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9230,27 +9230,1339 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.delinquent.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ここまで残っちまったな。ま、痛いのは後で考えるわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="281" ht="40" customHeight="1">
+      <c r="A281" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">相手は誰だ? ま、来た奴から順にぶっ倒すだけだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="282" ht="40" customHeight="1">
+      <c r="A282" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.delinquent.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.delinquent.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">いいぜいいぜ、次々来いよ。まとめて相手してやるって</t>
+        </is>
+      </c>
+    </row>
+    <row r="283" ht="40" customHeight="1">
+      <c r="A283" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">一人ぶっ倒したー! …はぁ、まだいけるっしょ。次、出てこいよー</t>
+        </is>
+      </c>
+    </row>
+    <row r="284" ht="40" customHeight="1">
+      <c r="A284" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.delinquent.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.delinquent.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ふう、一丁上がり。でもまだ終わってねえぞ。次、さっさと来い</t>
+        </is>
+      </c>
+    </row>
+    <row r="285" ht="40" customHeight="1">
+      <c r="A285" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">三人で勝ったぜ！ いやー、最高の気分だな</t>
+        </is>
+      </c>
+    </row>
+    <row r="286" ht="40" customHeight="1">
+      <c r="A286" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.delinquent.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.delinquent.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">仲間がいたから全然余裕だったっての。まあ、ちょっとは焦ったけどな</t>
+        </is>
+      </c>
+    </row>
+    <row r="287" ht="40" customHeight="1">
+      <c r="A287" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">MVPねえ。まあもらっとくけどさ、一人じゃ盛り上がんねえよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="288" ht="40" customHeight="1">
+      <c r="A288" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.delinquent.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.delinquent.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">次は全員で暴れて、全員で勝つ。そうじゃなきゃつまんねえ</t>
+        </is>
+      </c>
+    </row>
+    <row r="289" ht="40" customHeight="1">
+      <c r="A289" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">いやー次から次に来んのな。途中から面白くなっちゃったよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="290" ht="40" customHeight="1">
+      <c r="A290" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.delinquent.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.delinquent.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">何人だっけ？ まあいいや、全員倒したし。あたしの勝ちってことで</t>
+        </is>
+      </c>
+    </row>
+    <row r="291" ht="40" customHeight="1">
+      <c r="A291" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">いえ〜い！ 優勝〜！ 最高じゃん！</t>
+        </is>
+      </c>
+    </row>
+    <row r="292" ht="40" customHeight="1">
+      <c r="A292" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.delinquent.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.delinquent.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ひゃっほ〜！ やったぜ〜！</t>
+        </is>
+      </c>
+    </row>
+    <row r="293" ht="40" customHeight="1">
+      <c r="A293" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postLose.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">マジかー、負けたわ。ま、次があるし</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="40" customHeight="1">
+      <c r="A294" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.delinquent.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postLose.delinquent.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">しゃーねえな。次だ次</t>
+        </is>
+      </c>
+    </row>
+    <row r="295" ht="40" customHeight="1">
+      <c r="A295" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postMatchWin.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">いえーい！ 楽勝楽勝〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="296" ht="40" customHeight="1">
+      <c r="A296" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.delinquent.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postMatchWin.delinquent.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ノリノリだぜ！ 次も行くぞ〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="297" ht="40" customHeight="1">
+      <c r="A297" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postWin.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">楽しかったぜ〜。またやりてえな</t>
+        </is>
+      </c>
+    </row>
+    <row r="298" ht="40" customHeight="1">
+      <c r="A298" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.delinquent.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postWin.delinquent.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まあまあ良かったんじゃね？</t>
+        </is>
+      </c>
+    </row>
+    <row r="299" ht="40" customHeight="1">
+      <c r="A299" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">うっひょ〜決勝じゃん！ やるっきゃねえ！</t>
+        </is>
+      </c>
+    </row>
+    <row r="300" ht="40" customHeight="1">
+      <c r="A300" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.delinquent.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.delinquent.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">最後だし、全力で暴れるぜ！</t>
+        </is>
+      </c>
+    </row>
+    <row r="301" ht="40" customHeight="1">
+      <c r="A301" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">よーし、パパッとやっちまうか</t>
+        </is>
+      </c>
+    </row>
+    <row r="302" ht="40" customHeight="1">
+      <c r="A302" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.delinquent.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.delinquent.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">気楽にいこうぜ。でも手は抜かねえけど</t>
+        </is>
+      </c>
+    </row>
+    <row r="303" ht="40" customHeight="1">
+      <c r="A303" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">summon.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">マジ？ ウケる。まあ出てやるよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="304" ht="40" customHeight="1">
+      <c r="A304" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.delinquent.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">summon.delinquent.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ま、暴れる場所があるなら出るっしょ</t>
+        </is>
+      </c>
+    </row>
+    <row r="305" ht="40" customHeight="1">
+      <c r="A305" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">最高だぜ！楽しもうや！</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" ht="40" customHeight="1">
+      <c r="A306" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.delinquent.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">delinquent.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">へぇ、派手な舞台じゃん！せっかくだし楽しもっかな！</t>
+        </is>
+      </c>
+    </row>
+    <row r="307" ht="40" customHeight="1">
+      <c r="A307" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">マジかよ……！ やべえ、勝っちまった……！ 最高だ！</t>
+        </is>
+      </c>
+    </row>
+    <row r="308" ht="40" customHeight="1">
+      <c r="A308" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">よう、暇だから殴りに来たぜ</t>
+        </is>
+      </c>
+    </row>
+    <row r="309" ht="40" customHeight="1">
+      <c r="A309" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.delinquent.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">delinquent.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">面白えことしようぜ。対抗戦だ対抗戦</t>
+        </is>
+      </c>
+    </row>
+    <row r="310" ht="40" customHeight="1">
+      <c r="A310" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">は？ 逃げんの？ ダッセー</t>
+        </is>
+      </c>
+    </row>
+    <row r="311" ht="40" customHeight="1">
+      <c r="A311" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.delinquent.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">delinquent.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ま、ビビるのもわかるけどな。またな</t>
+        </is>
+      </c>
+    </row>
+    <row r="312" ht="40" customHeight="1">
+      <c r="A312" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ま、こういう日もあるっしょ。次だ次！</t>
+        </is>
+      </c>
+    </row>
+    <row r="313" ht="40" customHeight="1">
+      <c r="A313" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.delinquent.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.delinquent.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">くっそー、やられた。次は倍返しだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="314" ht="40" customHeight="1">
+      <c r="A314" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">いえーい！ 圧勝だぜ〜！</t>
+        </is>
+      </c>
+    </row>
+    <row r="315" ht="40" customHeight="1">
+      <c r="A315" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.delinquent.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.delinquent.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">面白かったぜ！ またかかって来いよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="316" ht="40" customHeight="1">
+      <c r="A316" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">よっしゃあ！ 勝った勝った！ 打ち上げだ打ち上げ！</t>
+        </is>
+      </c>
+    </row>
+    <row r="317" ht="40" customHeight="1">
+      <c r="A317" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">delinquent.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">よっしゃ〜！ まだまだいけるぜ〜！</t>
+        </is>
+      </c>
+    </row>
+    <row r="318" ht="40" customHeight="1">
+      <c r="A318" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.easygoing[3]</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">delinquent.easygoing[3]</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">いえーい！ 圧勝〜！ 打ち上げ行くぞ〜！</t>
+        </is>
+      </c>
+    </row>
+    <row r="319" ht="40" customHeight="1">
+      <c r="A319" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">最高だぜ！みんなありがとな！</t>
+        </is>
+      </c>
+    </row>
+    <row r="320" ht="40" customHeight="1">
+      <c r="A320" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">フリーもそろそろ飽きたんでな。世話になるぜ</t>
+        </is>
+      </c>
+    </row>
+    <row r="321" ht="40" customHeight="1">
+      <c r="A321" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">easygoing.delinquent[1]</t>
-        </is>
-      </c>
-      <c r="E280" t="inlineStr" s="2">
+      <c r="D321" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F280" t="inlineStr" s="3">
+      <c r="F321" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">スカウトってのも、けっこう悪い気しねーな。やる気出てきたっ！</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H280"/>
+  <autoFilter ref="A1:H321"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/ヤンキー×お気楽.xlsx
+++ b/セリフ編集/キャラタイプ別/ヤンキー×お気楽.xlsx
@@ -262,7 +262,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H321"/>
+  <dimension ref="A1:H323"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -921,7 +921,7 @@
       </c>
       <c r="F20" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">モテモテじゃん、アタシ。まー当然だけど</t>
+          <t xml:space="preserve">モテモテじゃん、私。まー当然だけど</t>
         </is>
       </c>
     </row>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="F29" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あたしを切ったの、ちょっと早まったんじゃねえの?</t>
+          <t xml:space="preserve">私を切ったの、ちょっと早まったんじゃねえの？</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="F40" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お疲れさん♪ あたしいくぜ</t>
+          <t xml:space="preserve">お疲れさん♪ 私いくぜ</t>
         </is>
       </c>
     </row>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="F41" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここからはあたしの出番だ♪</t>
+          <t xml:space="preserve">ここからは私の出番だ♪</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="F42" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{partner}〜わりぃ…あたし、決められちった…</t>
+          <t xml:space="preserve">{partner}〜わりぃ…私、決められちった…</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="F44" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{partner}〜お疲れさん！ あたしら息ぴったりだったろ？</t>
+          <t xml:space="preserve">{partner}〜お疲れさん！ 私ら息ぴったりだったろ？</t>
         </is>
       </c>
     </row>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="F68" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なあ社長、あの人と当ててくれない?</t>
+          <t xml:space="preserve">なあ社長、あの人と当ててくれない？</t>
         </is>
       </c>
     </row>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="F75" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お、あたし? いいよ、やろうやろう。</t>
+          <t xml:space="preserve">お、私？ いいよ、やろうやろう。</t>
         </is>
       </c>
     </row>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="F78" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決着つかずか。ちょうどいいんじゃね?</t>
+          <t xml:space="preserve">決着つかずか。ちょうどいいんじゃね？</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="F80" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだやんの? あたしはもういいよ。</t>
+          <t xml:space="preserve">まだやんの？ 私はもういいよ。</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="F100" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おいおい…邪魔だっての？さすがに ひどくない？</t>
+          <t xml:space="preserve">おいおい…邪魔だっての？さすがにひどくない？</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3833,7 @@
       </c>
       <c r="F111" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">残るぜ!ここの雰囲気、気に入ってるからな!</t>
+          <t xml:space="preserve">残るぜ！ここの雰囲気、気に入ってるからな！</t>
         </is>
       </c>
     </row>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="F128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長〜、あたしらの子のこと、たまには可愛がってやってくれません?</t>
+          <t xml:space="preserve">社長〜、私らの子のこと、たまには可愛がってやってくれません？</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       </c>
       <c r="F129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長〜、次のメイン、あたしらで暴れさせてくれません?</t>
+          <t xml:space="preserve">社長〜、次のメイン、私らで暴れさせてくれません？</t>
         </is>
       </c>
     </row>
@@ -4445,7 +4445,7 @@
       </c>
       <c r="F130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長〜、お給料の件、ちょっと色つけてくんないっすかね〜?</t>
+          <t xml:space="preserve">社長〜、お給料の件、ちょっと色つけてくんないっすかね〜？</t>
         </is>
       </c>
     </row>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長〜、あたしらの頑張り、たまには口に出してくれませんかね〜?</t>
+          <t xml:space="preserve">社長〜、私らの頑張り、たまには口に出してくれませんかね〜？</t>
         </is>
       </c>
     </row>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マジっすか、社長ありがとう〜! 嬉しいっすね。</t>
+          <t xml:space="preserve">マジっすか、社長ありがとう〜！ 嬉しいっすね。</t>
         </is>
       </c>
     </row>
@@ -4605,7 +4605,7 @@
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マジですか? 社長ありがとう! 暴れさせてもらいますね〜!</t>
+          <t xml:space="preserve">マジですか？ 社長ありがとう！ 暴れさせてもらいますね〜！</t>
         </is>
       </c>
     </row>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">へぇ、そっちっすか? まあ、ありがたいっすけど〜。</t>
+          <t xml:space="preserve">へぇ、そっちっすか？ まあ、ありがたいっすけど〜。</t>
         </is>
       </c>
     </row>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マジで上げてくれんすか?! 社長太っ腹〜! みんなにも言っときます!</t>
+          <t xml:space="preserve">マジで上げてくれんすか？！ 社長太っ腹〜！ みんなにも言っときます！</t>
         </is>
       </c>
     </row>
@@ -4797,7 +4797,7 @@
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マジっすか〜、社長に褒められちゃった〜! ありがとうございます。</t>
+          <t xml:space="preserve">マジっすか〜、社長に褒められちゃった〜！ ありがとうございます。</t>
         </is>
       </c>
     </row>
@@ -4893,7 +4893,7 @@
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え、気にしてました? ごめんなさ〜い、次は誘いますんで〜。</t>
+          <t xml:space="preserve">え、気にしてました？ ごめんなさ〜い、次は誘いますんで〜。</t>
         </is>
       </c>
     </row>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やった〜、社長わかってる〜! 引き続き暴れまっす!</t>
+          <t xml:space="preserve">やった〜、社長わかってる〜！ 引き続き暴れまっす！</t>
         </is>
       </c>
     </row>
@@ -5085,7 +5085,7 @@
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ〜ばれてました? すんませ〜ん、明日から出まっす。</t>
+          <t xml:space="preserve">あ〜、バレてました？ すんませ〜ん、明日から出まっす。</t>
         </is>
       </c>
     </row>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マジっすか〜、社長太っ腹! 助かります〜。</t>
+          <t xml:space="preserve">マジっすか〜、社長太っ腹！ 助かります〜。</t>
         </is>
       </c>
     </row>
@@ -5181,7 +5181,7 @@
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えへ、バレてました〜? じゃお言葉に甘えて休みまっす。</t>
+          <t xml:space="preserve">えへ、バレてました〜？ じゃお言葉に甘えて休みまっす。</t>
         </is>
       </c>
     </row>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えー、そんな話してました? まあ注意しときますんで〜。</t>
+          <t xml:space="preserve">えー、そんな話してました？ まあ注意しときますんで〜。</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お〜、続けていいんすか〜! やった〜!</t>
+          <t xml:space="preserve">お〜、続けていいんすか〜！ やった〜！</t>
         </is>
       </c>
     </row>
@@ -5533,7 +5533,7 @@
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あれ、あたしじゃなくて子たち優先っすか〜? まあありがたいっす。</t>
+          <t xml:space="preserve">あれ、私じゃなくて子たち優先っすか〜？ まあありがたいっす。</t>
         </is>
       </c>
     </row>
@@ -6116,7 +6116,7 @@
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">autumnWarChampion.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6141,14 +6141,14 @@
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">終わった瞬間「もう1ラウンドくれ！」って叫びそうになった！</t>
+          <t xml:space="preserve">団体戦って悪くないな。みんなで勝つと気分がいい。</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6163,7 +6163,7 @@
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">bestMatch.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6173,14 +6173,14 @@
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンの響き、たまんねえ！ もっと楽しむぜ！</t>
+          <t xml:space="preserve">終わった瞬間「もう1ラウンドくれ！」って叫びそうになった！</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6195,7 +6195,7 @@
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">champion.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6205,14 +6205,14 @@
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最っ高に楽しい選手人生だったぜ！ みんなありがとな！ プロレス最高！</t>
+          <t xml:space="preserve">チャンピオンの響き、たまんねえ！ もっと楽しむぜ！</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">hallOfFame.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6237,14 +6237,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うおお！ MVP！ いい響きじゃん！</t>
+          <t xml:space="preserve">最っ高に楽しい選手人生だったぜ！ みんなありがとな！ プロレス最高！</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">mvp.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6269,14 +6269,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うっそだろ！？ まあいいや、もらえるもんはもらっとく！</t>
+          <t xml:space="preserve">うおお！ MVP！ いい響きじゃん！</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6286,12 +6286,12 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[1]</t>
+          <t xml:space="preserve">rookie.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6301,14 +6301,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おーっ、ドームか。まぁやるだけよ</t>
+          <t xml:space="preserve">うっそだろ！？ まあいいや、もらえるもんはもらっとく！</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6318,12 +6318,12 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[2]</t>
+          <t xml:space="preserve">springTagChampion.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6333,14 +6333,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんつーか、あんま緊張しねーな。やるべ</t>
+          <t xml:space="preserve">相棒となら、面倒な相手でもなんとかなるもんだな。</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.delinquent.easygoing[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6355,7 +6355,7 @@
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[3]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6365,14 +6365,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いつも通りだろ。気楽に行こうぜ</t>
+          <t xml:space="preserve">おーっ、ドームか。まぁやるだけよ</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6397,14 +6397,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マジで満員かよ! やっべ、嬉しくて笑えてきたわ</t>
+          <t xml:space="preserve">なんつーか、あんま緊張しねーな。やるべ</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.delinquent.easygoing[3]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6414,12 +6414,12 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[2]</t>
+          <t xml:space="preserve">delinquent.easygoing[3]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6429,14 +6429,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">観客全員ぶち上がってたな! 気持ち良かったぜ</t>
+          <t xml:space="preserve">いつも通りだろ。気楽に行こうぜ</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.delinquent.easygoing[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[3]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6461,14 +6461,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こういう日もあんだな、人生ってよ</t>
+          <t xml:space="preserve">マジで満員かよ！ やっべ、嬉しくて笑えてきたわ</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6478,29 +6478,29 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんか急にキタわ！掴めた感じ！</t>
+          <t xml:space="preserve">観客全員ぶち上がってたな！ 気持ち良かったぜ</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.delinquent.easygoing[3]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6510,29 +6510,29 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[3]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あいつ最高！一緒だとテンション上がるわ！</t>
+          <t xml:space="preserve">こういう日もあんだな、人生ってよ</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">N1.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6557,14 +6557,14 @@
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あー疲れた。ちょい休むわ</t>
+          <t xml:space="preserve">なんか急にキタわ！掴めた感じ！</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6579,7 +6579,7 @@
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">N2.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6589,14 +6589,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンが盛り上がってんの最高じゃん！</t>
+          <t xml:space="preserve">あいつ最高！一緒だとテンション上がるわ！</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">N3.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6621,14 +6621,14 @@
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もーいいわ。考えさせてくれ</t>
+          <t xml:space="preserve">あー疲れた。ちょい休むわ</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6643,7 +6643,7 @@
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">N4.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6653,14 +6653,14 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あー…いや、なんでもねー。平気平気</t>
+          <t xml:space="preserve">ファンが盛り上がってんの最高じゃん！</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6670,29 +6670,29 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">N5_low.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やった！ラッキー！</t>
+          <t xml:space="preserve">もーいいわ。考えさせてくれ</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6702,29 +6702,29 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">N5_warning.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">合宿だー！ 盛り上がっていくぞー！</t>
+          <t xml:space="preserve">あー…いや、なんでもねー。平気平気</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">bonus.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6749,14 +6749,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見てくれてたんだ？ じゃ、もうちょいやるか！</t>
+          <t xml:space="preserve">やった！ラッキー！</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">camp.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6781,14 +6781,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おっしゃ！元気出た！やってやるわ！</t>
+          <t xml:space="preserve">合宿だー！ 盛り上がっていくぞー！</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">encourage_high_trust.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6813,14 +6813,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えー。せっかく楽しくやってたのに</t>
+          <t xml:space="preserve">見てくれてたんだ？ じゃ、もうちょいやるか！</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6835,7 +6835,7 @@
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">encourage.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6845,14 +6845,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テレビ！？ みんな見てるー？</t>
+          <t xml:space="preserve">おっしゃ！元気出た！やってやるわ！</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6867,7 +6867,7 @@
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">faction_decree.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6877,14 +6877,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うぇーい！飲むぞ〜！</t>
+          <t xml:space="preserve">えー。せっかく楽しくやってたのに</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">media.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6909,14 +6909,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">バカンスだー！戻ったら本気出すから！</t>
+          <t xml:space="preserve">テレビ！？ みんな見てるー？</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">party.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6941,14 +6941,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マジか！すぐ治してくる！</t>
+          <t xml:space="preserve">うぇーい！飲むぞ〜！</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">refresh_leave.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -6973,14 +6973,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マンツーマン！？ 超贅沢じゃん！</t>
+          <t xml:space="preserve">バカンスだー！戻ったら本気出すから！</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -6990,12 +6990,12 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">special_treatment.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7005,14 +7005,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テレビ出んの！？ 最高じゃん！</t>
+          <t xml:space="preserve">マジか！すぐ治してくる！</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">trainer.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7037,14 +7037,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">他所から話来たんだけど！ちょっと嬉しくね？</t>
+          <t xml:space="preserve">マンツーマン！？ 超贅沢じゃん！</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">E1.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7069,14 +7069,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はは…今日はサボるわ…</t>
+          <t xml:space="preserve">テレビ出んの！？ 最高じゃん！</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">E6.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7101,14 +7101,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習な…うーん、今日はパスで</t>
+          <t xml:space="preserve">他所から話来たんだけど！ちょっと嬉しくね？</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">S_boycott.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7133,14 +7133,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（いつもの軽口が消え、「なぁ、ちょっとさぁ…」と珍しく愚痴をこぼしている）</t>
+          <t xml:space="preserve">はは…今日はサボるわ…</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">S_boycott.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7165,14 +7165,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに「最近ちょい考えることあってさ」と珍しく真面目な投稿）</t>
+          <t xml:space="preserve">練習な…うーん、今日はパスで</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">S_grumble.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7197,14 +7197,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">タイトルマッチ組めよ！やる気あんだからさ！</t>
+          <t xml:space="preserve">（いつもの軽口が消え、「なぁ、ちょっとさぁ…」と珍しく愚痴をこぼしている）</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7219,7 +7219,7 @@
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">S_sns.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7229,14 +7229,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あいつとやらせろよ！ケリつけてやる！</t>
+          <t xml:space="preserve">（SNSに「最近ちょい考えることあってさ」と珍しく真面目な投稿）</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">S1.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7261,14 +7261,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">無理！限界！休ませて！</t>
+          <t xml:space="preserve">タイトルマッチ組めよ！やる気あんだからさ！</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7283,7 +7283,7 @@
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">S2.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7293,14 +7293,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう無理！ちゃんと話し合えよ！</t>
+          <t xml:space="preserve">あいつとやらせろよ！ケリつけてやる！</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">S3.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7325,14 +7325,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あー…いや、なんでもねえって（笑ってはいるが、目が笑っていない）</t>
+          <t xml:space="preserve">無理！限界！休ませて！</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7347,7 +7347,7 @@
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">S4_direct.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7357,14 +7357,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">特訓すんぞ！もっと強くなりてーんだよ！</t>
+          <t xml:space="preserve">もう無理！ちゃんと話し合えよ！</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">S4_silent.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7389,14 +7389,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">後輩の面倒見るわ！任せとけ！</t>
+          <t xml:space="preserve">あー…いや、なんでもねえって（笑ってはいるが、目が笑っていない）</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7406,12 +7406,12 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">S5.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7421,14 +7421,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いった！やっちまったけど、すぐ治すから！</t>
+          <t xml:space="preserve">特訓すんぞ！もっと強くなりてーんだよ！</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7438,12 +7438,12 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">S6.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7453,14 +7453,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あいつマジ無理！もう顔も見たくねえ！</t>
+          <t xml:space="preserve">後輩の面倒見るわ！任せとけ！</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7475,7 +7475,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">B1.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7485,14 +7485,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やんのか！？ 売られたケンカは買うぜ！</t>
+          <t xml:space="preserve">いった！やっちまったけど、すぐ治すから！</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">B2_fighter1.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7517,14 +7517,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">コラボか。なんか面白そうじゃん</t>
+          <t xml:space="preserve">あいつマジ無理！もう顔も見たくねえ！</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">B2_fighter2.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7549,14 +7549,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">CM撮影！？ 楽しそうじゃん！</t>
+          <t xml:space="preserve">やんのか！？ 売られたケンカは買うぜ！</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">B4_brand.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7581,14 +7581,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンと直接会えるのいいじゃん！ 楽しみ！</t>
+          <t xml:space="preserve">コラボか。なんか面白そうじゃん</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7603,7 +7603,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">B4_cm.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7613,14 +7613,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ランウェイか。めっちゃ目立てそうじゃん！</t>
+          <t xml:space="preserve">CM撮影！？ 楽しそうじゃん！</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7635,7 +7635,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">B4_fan.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7645,14 +7645,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">グラビアか。まぁ、派手にやってやる</t>
+          <t xml:space="preserve">ファンと直接会えるのいいじゃん！ 楽しみ！</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7667,7 +7667,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">B4_fashion.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7677,14 +7677,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テレビで暴れてやる！ 楽しみ！</t>
+          <t xml:space="preserve">ランウェイか。めっちゃ目立てそうじゃん！</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7699,7 +7699,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">B4_gravure.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7709,14 +7709,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テレビ！？ マジ！？ やったー！</t>
+          <t xml:space="preserve">グラビアか。まぁ、派手にやってやる</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7726,29 +7726,29 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[1]</t>
+          <t xml:space="preserve">B4_variety.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しくやろうぜ！退屈なのは嫌いだからな！</t>
+          <t xml:space="preserve">テレビで暴れてやる！ 楽しみ！</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7758,29 +7758,29 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[1]</t>
+          <t xml:space="preserve">B4.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よっ、よろしくな! 楽しくやろうぜ</t>
+          <t xml:space="preserve">テレビ！？ マジ！？ やったー！</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7790,7 +7790,7 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
@@ -7805,14 +7805,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よっしゃー！新天地だ！暴れるぞ！</t>
+          <t xml:space="preserve">楽しくやろうぜ！退屈なのは嫌いだからな！</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
@@ -7837,14 +7837,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よっしゃー！楽しくやろうぜ！</t>
+          <t xml:space="preserve">よっ、よろしくな！ 楽しくやろうぜ</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="12">
@@ -7869,14 +7869,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やっちまったぜ〜 まぁすぐ戻るわ</t>
+          <t xml:space="preserve">よっしゃー！新天地だ！暴れるぞ！</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7886,12 +7886,12 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7901,14 +7901,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しくやろうぜ！退屈なのは嫌いだからな！</t>
+          <t xml:space="preserve">よっしゃー！楽しくやろうぜ！</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7933,14 +7933,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よっ、よろしくな! 楽しくやろうぜ</t>
+          <t xml:space="preserve">やっちまったぜ〜 まぁすぐ戻るわ</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7955,7 +7955,7 @@
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">draftInterest.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -7965,14 +7965,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">フリーもそろそろ飽きたんでな。世話になるぜ</t>
+          <t xml:space="preserve">楽しくやろうぜ！退屈なのは嫌いだからな！</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -7987,7 +7987,7 @@
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">draftJoin.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -7997,14 +7997,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よっしゃー！新天地だ！暴れるぞ！</t>
+          <t xml:space="preserve">よっ、よろしくな！ 楽しくやろうぜ</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8019,7 +8019,7 @@
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">faGreeting.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8029,14 +8029,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よっしゃー！楽しくやろうぜ！</t>
+          <t xml:space="preserve">フリーもそろそろ飽きたんでな。世話になるぜ</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">faSigning.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8061,14 +8061,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お、今日は体が軽ぃな。もう一本いこうぜ</t>
+          <t xml:space="preserve">よっしゃー！新天地だ！暴れるぞ！</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8083,7 +8083,7 @@
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">faWelcome.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8093,14 +8093,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体がだりぃわ。今日やっても、ザルに水だろ</t>
+          <t xml:space="preserve">よっしゃー！楽しくやろうぜ！</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8125,14 +8125,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんか今日、乗んねーな。ま、動けてるからいっか</t>
+          <t xml:space="preserve">お、今日は体が軽ぃな。もう一本いこうぜ</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8147,7 +8147,7 @@
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">heatSelf.heavy.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8157,14 +8157,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やっちまったぜ〜 まぁすぐ戻るわ</t>
+          <t xml:space="preserve">体がだりぃわ。今日やっても、ザルに水だろ</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">heatSelf.warm.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8189,14 +8189,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ、こんなもんか。元気でやれよ〜</t>
+          <t xml:space="preserve">なんか今日、乗んねーな。ま、動けてるからいっか</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8211,7 +8211,7 @@
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">injury.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8221,14 +8221,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おじゃまー！暴れさせてもらうぜ！</t>
+          <t xml:space="preserve">やっちまったぜ〜 まぁすぐ戻るわ</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8243,7 +8243,7 @@
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">release.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8253,14 +8253,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">スカウトってのも、けっこう悪い気しねーな。やる気出てきたっ！</t>
+          <t xml:space="preserve">まぁ、こんなもんか。元気でやれよ〜</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8275,7 +8275,7 @@
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">rentalGreeting.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8285,14 +8285,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそー！悔しい！でも次やってやるからな！</t>
+          <t xml:space="preserve">おじゃまー！暴れさせてもらうぜ！</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">scoutGreeting.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8317,14 +8317,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだまだ渡さねーよ！最高！</t>
+          <t xml:space="preserve">スカウトってのも、けっこう悪い気しねーな。やる気出てきたっ！</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8339,7 +8339,7 @@
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8349,14 +8349,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそー！でもまだ終わってねえから！</t>
+          <t xml:space="preserve">くそー！悔しい！でも次やってやるからな！</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">titleDefense.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8381,14 +8381,14 @@
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンだぜー！最高だろ！</t>
+          <t xml:space="preserve">まだまだ渡さねーよ！最高！</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8398,12 +8398,12 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[1]</t>
+          <t xml:space="preserve">titleLoss.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8413,14 +8413,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ、こんなもんか。元気でやれよ〜</t>
+          <t xml:space="preserve">くそー！でもまだ終わってねえから！</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8430,12 +8430,12 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[1]</t>
+          <t xml:space="preserve">titleWin.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8445,14 +8445,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おじゃまー！暴れさせてもらうぜ！</t>
+          <t xml:space="preserve">チャンピオンだぜー！最高だろ！</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8462,7 +8462,7 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
@@ -8477,14 +8477,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそー！悔しい！でも次やってやるからな！</t>
+          <t xml:space="preserve">まぁ、こんなもんか。元気でやれよ〜</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="12">
@@ -8509,14 +8509,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだまだ渡さねーよ！最高！</t>
+          <t xml:space="preserve">おじゃまー！暴れさせてもらうぜ！</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="12">
@@ -8541,14 +8541,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそー！でもまだ終わってねえから！</t>
+          <t xml:space="preserve">くそー！悔しい！でも次やってやるからな！</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="12">
@@ -8573,14 +8573,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンだぜー！最高だろ！</t>
+          <t xml:space="preserve">まだまだ渡さねーよ！最高！</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8590,29 +8590,29 @@
       </c>
       <c r="C260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う〜ん、ちょい合わねぇかもな…</t>
+          <t xml:space="preserve">くそー！でもまだ終わってねえから！</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8622,29 +8622,29 @@
       </c>
       <c r="C261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あれ〜、最近ちょい素っ気なくね？</t>
+          <t xml:space="preserve">チャンピオンだぜー！最高だろ！</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8659,7 +8659,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">bond_39_down.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8669,14 +8669,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">んー、なんか空気変わった気ぃすんだけど</t>
+          <t xml:space="preserve">う〜ん、ちょい合わねぇかもな…</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">bond_59_down.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8701,14 +8701,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">つるんでると楽しいんだわ、まじで</t>
+          <t xml:space="preserve">あれ〜、最近ちょい素っ気なくね？</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">bond_59_down.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8733,14 +8733,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一生の仲間だぜ。間違いない</t>
+          <t xml:space="preserve">んー、なんか空気変わった気ぃすんだけど</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">bond_60_up.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8765,14 +8765,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">熱い関係も一段落かぁ。ちっと寂しいな</t>
+          <t xml:space="preserve">つるんでると楽しいんだわ、まじで</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">bond_80_up.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8797,14 +8797,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ因縁も永遠じゃねぇよな〜</t>
+          <t xml:space="preserve">一生の仲間だぜ。間違いない</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8819,7 +8819,7 @@
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">rivalry_29_down.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8829,14 +8829,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やり合うの、ワクワクすんだよな</t>
+          <t xml:space="preserve">熱い関係も一段落かぁ。ちっと寂しいな</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8851,7 +8851,7 @@
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">rivalry_29_down.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8861,14 +8861,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">本気でやり合いてぇ相手なんて、そうはいねぇよ</t>
+          <t xml:space="preserve">まぁ因縁も永遠じゃねぇよな〜</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8883,7 +8883,7 @@
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">rivalry_30_up.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -8893,14 +8893,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">へへ、考えると自然に気合入るんだわ</t>
+          <t xml:space="preserve">やり合うの、ワクワクすんだよな</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8915,7 +8915,7 @@
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">rivalry_50_up.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -8925,14 +8925,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この試合が一番楽しいんだわ。ずっと続けばいいのにな</t>
+          <t xml:space="preserve">本気でやり合いてぇ相手なんて、そうはいねぇよ</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">rivalry_50_up.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -8957,14 +8957,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">運命のライバルってやつだろ。最高だぜ</t>
+          <t xml:space="preserve">へへ、考えると自然に気合入るんだわ</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -8979,7 +8979,7 @@
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">rivalry_70_up.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -8989,14 +8989,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここ最高〜！ みんなとやんの楽しいわ！</t>
+          <t xml:space="preserve">この試合が一番楽しいんだわ。ずっと続けばいいのにな</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9011,7 +9011,7 @@
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">rivalry_70_up.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9021,14 +9021,14 @@
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体、すげぇ居心地いいんだわ〜</t>
+          <t xml:space="preserve">運命のライバルってやつだろ。最高だぜ</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9043,7 +9043,7 @@
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">trust_above_75.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9053,14 +9053,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">さすがにこれは…笑えねぇかも</t>
+          <t xml:space="preserve">ここ最高〜！ みんなとやんの楽しいわ！</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9075,7 +9075,7 @@
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">trust_above_75.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9085,14 +9085,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あはは…って笑ってる場合じゃねぇよな、これ</t>
+          <t xml:space="preserve">この団体、すげぇ居心地いいんだわ〜</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9107,7 +9107,7 @@
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">trust_below_20.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9117,14 +9117,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う〜ん、最近ちっとモヤモヤすんだよなぁ…</t>
+          <t xml:space="preserve">さすがにこれは…笑えねぇかも</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">trust_below_20.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9149,14 +9149,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ大丈夫…だよな？ ちょい不安だけど</t>
+          <t xml:space="preserve">あはは…って笑ってる場合じゃねぇよな、これ</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[1]</t>
+          <t xml:space="preserve">trust_below_35.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9181,14 +9181,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">終わっちまったかー。まぁ次また来るっしょ</t>
+          <t xml:space="preserve">う〜ん、最近ちっとモヤモヤすんだよなぁ…</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9198,29 +9198,29 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">trust_below_35.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いやー身体ガタガタだわ。でも最後だし、暴れて終わろうぜ</t>
+          <t xml:space="preserve">まぁ大丈夫…だよな？ ちょい不安だけど</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9230,29 +9230,29 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで残っちまったな。ま、痛いのは後で考えるわ</t>
+          <t xml:space="preserve">終わっちまったかー。まぁ次また来るっしょ</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">preFinal.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9277,14 +9277,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手は誰だ? ま、来た奴から順にぶっ倒すだけだ</t>
+          <t xml:space="preserve">いやー身体ガタガタだわ。でも最後だし、暴れて終わろうぜ</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9299,7 +9299,7 @@
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">preFinal.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9309,14 +9309,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いいぜいいぜ、次々来いよ。まとめて相手してやるって</t>
+          <t xml:space="preserve">ここまで残っちまったな。ま、痛いのは後で考えるわ</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9331,7 +9331,7 @@
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">preMatch.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9341,14 +9341,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人ぶっ倒したー! …はぁ、まだいけるっしょ。次、出てこいよー</t>
+          <t xml:space="preserve">相手は誰だ？ ま、来た奴から順にぶっ倒すだけだ</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9363,7 +9363,7 @@
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">preMatch.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9373,14 +9373,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふう、一丁上がり。でもまだ終わってねえぞ。次、さっさと来い</t>
+          <t xml:space="preserve">いいぜいいぜ、次々来いよ。まとめて相手してやるって</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9390,12 +9390,12 @@
       </c>
       <c r="C285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">survivor.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9405,14 +9405,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で勝ったぜ！ いやー、最高の気分だな</t>
+          <t xml:space="preserve">一人ぶっ倒したー！ …はぁ、まだいけるっしょ。次、出てこいよー</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">survivor.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9437,14 +9437,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間がいたから全然余裕だったっての。まあ、ちょっとは焦ったけどな</t>
+          <t xml:space="preserve">ふう、一丁上がり。でもまだ終わってねえぞ。次、さっさと来い</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9459,7 +9459,7 @@
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">champion.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9469,14 +9469,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVPねえ。まあもらっとくけどさ、一人じゃ盛り上がんねえよ</t>
+          <t xml:space="preserve">三人で勝ったぜ！ いやー、最高の気分だな</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">champion.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9501,14 +9501,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次は全員で暴れて、全員で勝つ。そうじゃなきゃつまんねえ</t>
+          <t xml:space="preserve">仲間がいたから全然余裕だったっての。まあ、ちょっとは焦ったけどな</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9523,7 +9523,7 @@
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">defiant.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9533,14 +9533,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いやー次から次に来んのな。途中から面白くなっちゃったよ</t>
+          <t xml:space="preserve">MVPねえ。まあもらっとくけどさ、一人じゃ盛り上がんねえよ</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9555,7 +9555,7 @@
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">defiant.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9565,14 +9565,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人だっけ？ まあいいや、全員倒したし。あたしの勝ちってことで</t>
+          <t xml:space="preserve">次は全員で暴れて、全員で勝つ。そうじゃなきゃつまんねえ</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9582,12 +9582,12 @@
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">gauntlet.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9597,14 +9597,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いえ〜い！ 優勝〜！ 最高じゃん！</t>
+          <t xml:space="preserve">いやー次から次に来んのな。途中から面白くなっちゃったよ</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9614,12 +9614,12 @@
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">gauntlet.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9629,14 +9629,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ひゃっほ〜！ やったぜ〜！</t>
+          <t xml:space="preserve">何人だっけ？ まあいいや、全員倒したし。私の勝ちってことで</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9651,7 +9651,7 @@
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">champion.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9661,14 +9661,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マジかー、負けたわ。ま、次があるし</t>
+          <t xml:space="preserve">いえ〜い！ 優勝〜！ 最高じゃん！</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9683,7 +9683,7 @@
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">champion.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9693,14 +9693,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">しゃーねえな。次だ次</t>
+          <t xml:space="preserve">ひゃっほ〜！ やったぜ〜！</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9715,7 +9715,7 @@
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">postLose.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9725,14 +9725,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いえーい！ 楽勝楽勝〜</t>
+          <t xml:space="preserve">マジかー、負けたわ。ま、次があるし</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9747,7 +9747,7 @@
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">postLose.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9757,14 +9757,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ノリノリだぜ！ 次も行くぞ〜</t>
+          <t xml:space="preserve">しゃーねえな。次だ次</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">postMatchWin.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9789,14 +9789,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しかったぜ〜。またやりてえな</t>
+          <t xml:space="preserve">いえーい！ 楽勝楽勝〜</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">postMatchWin.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9821,14 +9821,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあまあ良かったんじゃね？</t>
+          <t xml:space="preserve">ノリノリだぜ！ 次も行くぞ〜</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9843,7 +9843,7 @@
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">postWin.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9853,14 +9853,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うっひょ〜決勝じゃん！ やるっきゃねえ！</t>
+          <t xml:space="preserve">楽しかったぜ〜。またやりてえな</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9875,7 +9875,7 @@
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">postWin.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -9885,14 +9885,14 @@
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最後だし、全力で暴れるぜ！</t>
+          <t xml:space="preserve">まあまあ良かったんじゃね？</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">preFinal.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -9917,14 +9917,14 @@
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よーし、パパッとやっちまうか</t>
+          <t xml:space="preserve">うっひょ〜決勝じゃん！ やるっきゃねえ！</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">preFinal.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -9949,14 +9949,14 @@
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">気楽にいこうぜ。でも手は抜かねえけど</t>
+          <t xml:space="preserve">最後だし、全力で暴れるぜ！</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -9971,7 +9971,7 @@
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">preMatch.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
@@ -9981,14 +9981,14 @@
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マジ？ ウケる。まあ出てやるよ</t>
+          <t xml:space="preserve">よーし、パパッとやっちまうか</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10003,7 +10003,7 @@
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">preMatch.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
@@ -10013,14 +10013,14 @@
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、暴れる場所があるなら出るっしょ</t>
+          <t xml:space="preserve">気楽にいこうぜ。でも手は抜かねえけど</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="C305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[1]</t>
+          <t xml:space="preserve">summon.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
@@ -10045,14 +10045,14 @@
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高だぜ！楽しもうや！</t>
+          <t xml:space="preserve">マジ？ ウケる。まあ出てやるよ</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10062,12 +10062,12 @@
       </c>
       <c r="C306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[2]</t>
+          <t xml:space="preserve">summon.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
@@ -10077,14 +10077,14 @@
       </c>
       <c r="F306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">へぇ、派手な舞台じゃん！せっかくだし楽しもっかな！</t>
+          <t xml:space="preserve">ま、暴れる場所があるなら出るっしょ</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="C307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D307" t="inlineStr" s="12">
@@ -10109,14 +10109,14 @@
       </c>
       <c r="F307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マジかよ……！ やべえ、勝っちまった……！ 最高だ！</t>
+          <t xml:space="preserve">最高だぜ！楽しもうや！</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10126,12 +10126,12 @@
       </c>
       <c r="C308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
@@ -10141,14 +10141,14 @@
       </c>
       <c r="F308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よう、暇だから殴りに来たぜ</t>
+          <t xml:space="preserve">へぇ、派手な舞台じゃん！せっかくだし楽しもっかな！</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="C309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[2]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
@@ -10173,14 +10173,14 @@
       </c>
       <c r="F309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">面白えことしようぜ。対抗戦だ対抗戦</t>
+          <t xml:space="preserve">マジかよ……！ やべえ、勝っちまった……！ 最高だ！</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10190,7 +10190,7 @@
       </c>
       <c r="C310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D310" t="inlineStr" s="12">
@@ -10205,14 +10205,14 @@
       </c>
       <c r="F310" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">は？ 逃げんの？ ダッセー</t>
+          <t xml:space="preserve">よう、暇だから殴りに来たぜ</t>
         </is>
       </c>
     </row>
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10222,7 +10222,7 @@
       </c>
       <c r="C311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D311" t="inlineStr" s="12">
@@ -10237,14 +10237,14 @@
       </c>
       <c r="F311" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、ビビるのもわかるけどな。またな</t>
+          <t xml:space="preserve">面白えことしようぜ。対抗戦だ対抗戦</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10254,12 +10254,12 @@
       </c>
       <c r="C312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
@@ -10269,14 +10269,14 @@
       </c>
       <c r="F312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、こういう日もあるっしょ。次だ次！</t>
+          <t xml:space="preserve">は？ 逃げんの？ ダッセー</t>
         </is>
       </c>
     </row>
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="C313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
@@ -10301,14 +10301,14 @@
       </c>
       <c r="F313" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くっそー、やられた。次は倍返しだ</t>
+          <t xml:space="preserve">ま、ビビるのもわかるけどな。またな</t>
         </is>
       </c>
     </row>
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10323,7 +10323,7 @@
       </c>
       <c r="D314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">result_lose.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E314" t="inlineStr" s="2">
@@ -10333,14 +10333,14 @@
       </c>
       <c r="F314" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いえーい！ 圧勝だぜ〜！</t>
+          <t xml:space="preserve">ま、こういう日もあるっしょ。次だ次！</t>
         </is>
       </c>
     </row>
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10355,7 +10355,7 @@
       </c>
       <c r="D315" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">result_lose.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E315" t="inlineStr" s="2">
@@ -10365,14 +10365,14 @@
       </c>
       <c r="F315" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">面白かったぜ！ またかかって来いよ</t>
+          <t xml:space="preserve">くっそー、やられた。次は倍返しだ</t>
         </is>
       </c>
     </row>
     <row r="316" ht="40" customHeight="1">
       <c r="A316" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
@@ -10382,12 +10382,12 @@
       </c>
       <c r="C316" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D316" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[1]</t>
+          <t xml:space="preserve">result_win.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E316" t="inlineStr" s="2">
@@ -10397,14 +10397,14 @@
       </c>
       <c r="F316" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よっしゃあ！ 勝った勝った！ 打ち上げだ打ち上げ！</t>
+          <t xml:space="preserve">いえーい！ 圧勝だぜ〜！</t>
         </is>
       </c>
     </row>
     <row r="317" ht="40" customHeight="1">
       <c r="A317" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
@@ -10414,12 +10414,12 @@
       </c>
       <c r="C317" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D317" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[2]</t>
+          <t xml:space="preserve">result_win.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E317" t="inlineStr" s="2">
@@ -10429,14 +10429,14 @@
       </c>
       <c r="F317" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よっしゃ〜！ まだまだいけるぜ〜！</t>
+          <t xml:space="preserve">面白かったぜ！ またかかって来いよ</t>
         </is>
       </c>
     </row>
     <row r="318" ht="40" customHeight="1">
       <c r="A318" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.easygoing[3]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B318" t="inlineStr" s="2">
@@ -10451,7 +10451,7 @@
       </c>
       <c r="D318" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[3]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E318" t="inlineStr" s="2">
@@ -10461,14 +10461,14 @@
       </c>
       <c r="F318" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いえーい！ 圧勝〜！ 打ち上げ行くぞ〜！</t>
+          <t xml:space="preserve">よっしゃあ！ 勝った勝った！ 打ち上げだ打ち上げ！</t>
         </is>
       </c>
     </row>
     <row r="319" ht="40" customHeight="1">
       <c r="A319" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B319" t="inlineStr" s="2">
@@ -10478,29 +10478,29 @@
       </c>
       <c r="C319" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D319" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E319" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F319" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高だぜ！みんなありがとな！</t>
+          <t xml:space="preserve">よっしゃ〜！ まだまだいけるぜ〜！</t>
         </is>
       </c>
     </row>
     <row r="320" ht="40" customHeight="1">
       <c r="A320" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.easygoing[3]</t>
         </is>
       </c>
       <c r="B320" t="inlineStr" s="2">
@@ -10510,59 +10510,123 @@
       </c>
       <c r="C320" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D320" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[3]</t>
         </is>
       </c>
       <c r="E320" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F320" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">フリーもそろそろ飽きたんでな。世話になるぜ</t>
+          <t xml:space="preserve">いえーい！ 圧勝〜！ 打ち上げ行くぞ〜！</t>
         </is>
       </c>
     </row>
     <row r="321" ht="40" customHeight="1">
       <c r="A321" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">最高だぜ！みんなありがとな！</t>
+        </is>
+      </c>
+    </row>
+    <row r="322" ht="40" customHeight="1">
+      <c r="A322" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">フリーもそろそろ飽きたんでな。世話になるぜ</t>
+        </is>
+      </c>
+    </row>
+    <row r="323" ht="40" customHeight="1">
+      <c r="A323" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
-      <c r="B321" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C321" t="inlineStr" s="2">
+      <c r="B323" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr" s="12">
+      <c r="D323" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
-      <c r="E321" t="inlineStr" s="2">
+      <c r="E323" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F321" t="inlineStr" s="3">
+      <c r="F323" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">スカウトってのも、けっこう悪い気しねーな。やる気出てきたっ！</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H321"/>
+  <autoFilter ref="A1:H323"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/ヤンキー×お気楽.xlsx
+++ b/セリフ編集/キャラタイプ別/ヤンキー×お気楽.xlsx
@@ -262,7 +262,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H323"/>
+  <dimension ref="A1:H330"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -3840,7 +3840,7 @@
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_accept.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">decline_accept.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -3865,14 +3865,14 @@
       </c>
       <c r="F112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おっしゃー！ さすが社長！ やる気出てきたぜ！</t>
+          <t xml:space="preserve">はいはい了解〜。落ちたもんはしゃーないっしょ。飯代くらいは残ってるし、まあ生きてけるって。</t>
         </is>
       </c>
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_hold.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">decline_hold.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -3897,14 +3897,14 @@
       </c>
       <c r="F113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まーいいか！ もらえるだけ儲けもんだぜ！</t>
+          <t xml:space="preserve">えっ、据え置き？ ……うわ、参ったな。こういうの、笑って受け取れないタイプなんだよね私。</t>
         </is>
       </c>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_open.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">decline_open.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -3929,14 +3929,14 @@
       </c>
       <c r="F114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あちゃー、マジかー。まーしゃーねーか。</t>
+          <t xml:space="preserve">あー、やっぱそういう話か。いいっていいって、言いにくそうな顔しなくても。で、いくら下がんの？</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_strict.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">decline_strict.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -3961,14 +3961,14 @@
       </c>
       <c r="F115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よー社長。{tenure}給料の話なんだけどさー。もうちょいくれよー。{record}</t>
+          <t xml:space="preserve">うわ、きっちり取るなあ。……あはは。……いや、笑えないやつだ、これ。</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_accept.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">decline_voluntary_accept.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -3993,14 +3993,14 @@
       </c>
       <c r="F116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あー、やっぱダメか。まーいいけどさ、いつか上げろよな？</t>
+          <t xml:space="preserve">おっけー、話が早い！ よし、これで気兼ねなく飯が食える。……いや食えるのか？ 食えるな。</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_hold.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">decline_voluntary_hold.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4025,14 +4025,14 @@
       </c>
       <c r="F117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いやー、ついにこの日が来ちまったっすね。じゃ、元気で。</t>
+          <t xml:space="preserve">えー、聞いてた？ 下げていいって言ったじゃん。……もー、断りにくいことすんなよなあ。</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_open.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">decline_voluntary_open.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -4057,14 +4057,14 @@
       </c>
       <c r="F118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう潮時っしょ。楽しかったっすよ、うん。じゃあ、失礼します。</t>
+          <t xml:space="preserve">言いにくそうな顔してるから、こっちから言うわ。下げていいよ。こういうのは、言った者勝ちだからね。</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4079,7 +4079,7 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">raise_accept.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -4089,14 +4089,14 @@
       </c>
       <c r="F119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">聞いてくれんの？ {record}なんつーか、マンネリなんだよな。新しいとこ行きてーんだ。</t>
+          <t xml:space="preserve">おっしゃー！ さすが社長！ やる気出てきたぜ！</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
@@ -4121,14 +4121,14 @@
       </c>
       <c r="F120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。{tenure}悪いけどさー、ちょっと外に出てみたいんだよね。</t>
+          <t xml:space="preserve">まーいいか！ もらえるだけ儲けもんだぜ！</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
@@ -4153,14 +4153,14 @@
       </c>
       <c r="F121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まーそうなるよなー。{tenure_farewell}{rivalry}元気でな！</t>
+          <t xml:space="preserve">あちゃー、マジかー。まーしゃーねーか。</t>
         </is>
       </c>
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4175,7 +4175,7 @@
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">raise_open.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
@@ -4185,14 +4185,14 @@
       </c>
       <c r="F122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悪いな社長。金の問題じゃねーんだよ。もう決めちまったから。</t>
+          <t xml:space="preserve">よー社長。{tenure}給料の話なんだけどさー。もうちょいくれよー。{record}</t>
         </is>
       </c>
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">raise_refuse.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
@@ -4217,370 +4217,370 @@
       </c>
       <c r="F123" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マジかよ。そこまでしてくれんの？ じゃーもうちょいいるか！</t>
+          <t xml:space="preserve">あー、やっぱダメか。まーいいけどさ、いつか上げろよな？</t>
         </is>
       </c>
     </row>
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">いやー、ついにこの日が来ちまったっすね。じゃ、元気で。</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="40" customHeight="1">
+      <c r="A125" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.delinquent.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.delinquent.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">もう潮時っしょ。楽しかったっすよ、うん。じゃあ、失礼します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="40" customHeight="1">
+      <c r="A126" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_listen.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">聞いてくれんの？ {record}なんつーか、マンネリなんだよな。新しいとこ行きてーんだ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="40" customHeight="1">
+      <c r="A127" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_open.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長。{tenure}悪いけどさー、ちょっと外に出てみたいんだよね。</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="40" customHeight="1">
+      <c r="A128" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_release.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まーそうなるよなー。{tenure_farewell}{rivalry}元気でな！</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="40" customHeight="1">
+      <c r="A129" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_fail.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">悪いな社長。金の問題じゃねーんだよ。もう決めちまったから。</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="40" customHeight="1">
+      <c r="A130" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_success.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">マジかよ。そこまでしてくれんの？ じゃーもうちょいいるか！</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="40" customHeight="1">
+      <c r="A131" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">NEGOTIATE_LINES.blocked.delinquent.easygoing[1]</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr" s="2">
+      <c r="B131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr" s="12">
+      <c r="D131" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">blocked.delinquent.easygoing[1]</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr" s="2">
+      <c r="E131" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr" s="3">
+      <c r="F131" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">おっ、引き抜きか！気持ちは嬉しいけどな、
 今の仲間が好きすぎて動けないわ！</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="40" customHeight="1">
-      <c r="A125" t="inlineStr" s="15">
+    <row r="132" ht="40" customHeight="1">
+      <c r="A132" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.fail.delinquent.easygoing[1]</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr" s="2">
+      <c r="B132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr" s="12">
+      <c r="D132" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fail.delinquent.easygoing[1]</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr" s="2">
+      <c r="E132" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr" s="3">
+      <c r="F132" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">ごめんな〜、今のとこが好きなんだよ！
 またな！</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="40" customHeight="1">
-      <c r="A126" t="inlineStr" s="15">
+    <row r="133" ht="40" customHeight="1">
+      <c r="A133" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.start.delinquent.easygoing[1]</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr" s="2">
+      <c r="B133" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr" s="12">
+      <c r="D133" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">start.delinquent.easygoing[1]</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr" s="2">
+      <c r="E133" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr" s="3">
+      <c r="F133" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">マジで！？ スカウト！？
 話聞かせてくれよ！</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="40" customHeight="1">
-      <c r="A127" t="inlineStr" s="15">
+    <row r="134" ht="40" customHeight="1">
+      <c r="A134" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.success.delinquent.easygoing[1]</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr" s="2">
+      <c r="B134" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr" s="12">
+      <c r="D134" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">success.delinquent.easygoing[1]</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr" s="2">
+      <c r="E134" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr" s="3">
+      <c r="F134" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">やったぜ！ 新しい団体！
 楽しみすぎて眠れねーよ！</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="40" customHeight="1">
-      <c r="A128" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.delinquent.easygoing[1]</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.delinquent.easygoing[1]</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長〜、私らの子のこと、たまには可愛がってやってくれません？</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="40" customHeight="1">
-      <c r="A129" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.delinquent.easygoing[1]</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.delinquent.easygoing[1]</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長〜、次のメイン、私らで暴れさせてくれません？</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="40" customHeight="1">
-      <c r="A130" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.delinquent.easygoing[1]</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.delinquent.easygoing[1]</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長〜、お給料の件、ちょっと色つけてくんないっすかね〜？</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="40" customHeight="1">
-      <c r="A131" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.delinquent.easygoing[1]</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.delinquent.easygoing[1]</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長〜、私らの頑張り、たまには口に出してくれませんかね〜？</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="40" customHeight="1">
-      <c r="A132" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.delinquent.easygoing[1]</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.delinquent.easygoing[1]</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">マジっすか、社長ありがとう〜！ 嬉しいっすね。</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="40" customHeight="1">
-      <c r="A133" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.delinquent.easygoing[1]</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.delinquent.easygoing[1]</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">あ、はい〜。まあ社長忙しいっすもんね。</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="40" customHeight="1">
-      <c r="A134" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.delinquent.easygoing[1]</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.delinquent.easygoing[1]</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">へぇ、別ルートっすか〜。まあ気持ちは受け取ります〜。</t>
-        </is>
-      </c>
-    </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
@@ -4605,14 +4605,14 @@
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マジですか？ 社長ありがとう！ 暴れさせてもらいますね〜！</t>
+          <t xml:space="preserve">社長〜、私らの子のこと、たまには可愛がってやってくれません？</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
@@ -4637,14 +4637,14 @@
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えぇ〜、つれないっすね〜。まあいいっすけど。</t>
+          <t xml:space="preserve">社長〜、次のメイン、私らで暴れさせてくれません？</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
@@ -4669,14 +4669,14 @@
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">へぇ、そっちっすか？ まあ、ありがたいっすけど〜。</t>
+          <t xml:space="preserve">社長〜、お給料の件、ちょっと色つけてくんないっすかね〜？</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
@@ -4701,14 +4701,14 @@
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マジで上げてくれんすか？！ 社長太っ腹〜！ みんなにも言っときます！</t>
+          <t xml:space="preserve">社長〜、私らの頑張り、たまには口に出してくれませんかね〜？</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4723,7 +4723,7 @@
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
@@ -4733,14 +4733,14 @@
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えぇ〜、ケチっすね〜。まあ次に期待してますんで〜。</t>
+          <t xml:space="preserve">マジっすか、社長ありがとう〜！ 嬉しいっすね。</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
@@ -4765,14 +4765,14 @@
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">へぇ、お金じゃないんすか〜。まあ気持ちは嬉しいっす〜。</t>
+          <t xml:space="preserve">あ、はい〜。まあ社長忙しいっすもんね。</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
@@ -4797,14 +4797,14 @@
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マジっすか〜、社長に褒められちゃった〜！ ありがとうございます。</t>
+          <t xml:space="preserve">へぇ、別ルートっすか〜。まあ気持ちは受け取ります〜。</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
@@ -4829,14 +4829,14 @@
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えぇ〜、つれないっすね〜。まあいいっすけど〜。</t>
+          <t xml:space="preserve">マジですか？ 社長ありがとう！ 暴れさせてもらいますね〜！</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
@@ -4861,14 +4861,14 @@
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">へぇ、別ルートっすか〜。まあ気持ちは受け取ります〜。</t>
+          <t xml:space="preserve">えぇ〜、つれないっすね〜。まあいいっすけど。</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
@@ -4893,14 +4893,14 @@
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え、気にしてました？ ごめんなさ〜い、次は誘いますんで〜。</t>
+          <t xml:space="preserve">へぇ、そっちっすか？ まあ、ありがたいっすけど〜。</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
@@ -4925,14 +4925,14 @@
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうござ〜っす、楽しんできまっす。</t>
+          <t xml:space="preserve">マジで上げてくれんすか？！ 社長太っ腹〜！ みんなにも言っときます！</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
@@ -4957,14 +4957,14 @@
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、そっかぁ〜、気をつけまっす。</t>
+          <t xml:space="preserve">えぇ〜、ケチっすね〜。まあ次に期待してますんで〜。</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
@@ -4989,14 +4989,14 @@
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうござ〜っす。</t>
+          <t xml:space="preserve">へぇ、お金じゃないんすか〜。まあ気持ちは嬉しいっす〜。</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
@@ -5021,14 +5021,14 @@
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えぇ〜、客ノッてたじゃないっすか〜。はい、控えまっす。</t>
+          <t xml:space="preserve">マジっすか〜、社長に褒められちゃった〜！ ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5043,7 +5043,7 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
@@ -5053,14 +5053,14 @@
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やった〜、社長わかってる〜！ 引き続き暴れまっす！</t>
+          <t xml:space="preserve">えぇ〜、つれないっすね〜。まあいいっすけど〜。</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5075,7 +5075,7 @@
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
@@ -5085,14 +5085,14 @@
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ〜、バレてました？ すんませ〜ん、明日から出まっす。</t>
+          <t xml:space="preserve">へぇ、別ルートっすか〜。まあ気持ちは受け取ります〜。</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
@@ -5117,14 +5117,14 @@
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マジっすか〜、社長太っ腹！ 助かります〜。</t>
+          <t xml:space="preserve">え、気にしてました？ ごめんなさ〜い、次は誘いますんで〜。</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
@@ -5149,14 +5149,14 @@
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">へぇ、メンバーケアっすか〜。まあありがたいっす。</t>
+          <t xml:space="preserve">ありがとうござ〜っす、楽しんできまっす。</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
@@ -5181,14 +5181,14 @@
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えへ、バレてました〜？ じゃお言葉に甘えて休みまっす。</t>
+          <t xml:space="preserve">あ、そっかぁ〜、気をつけまっす。</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
@@ -5213,14 +5213,14 @@
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いやいや、まだいけますって〜。</t>
+          <t xml:space="preserve">ありがとうござ〜っす。</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5235,7 +5235,7 @@
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
@@ -5245,14 +5245,14 @@
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">へぇ、メンバー優先っすか〜。助かりますね〜。</t>
+          <t xml:space="preserve">えぇ〜、客ノッてたじゃないっすか〜。はい、控えまっす。</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
@@ -5277,14 +5277,14 @@
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えー、そんな話してました？ まあ注意しときますんで〜。</t>
+          <t xml:space="preserve">やった〜、社長わかってる〜！ 引き続き暴れまっす！</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
@@ -5309,14 +5309,14 @@
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お〜、放っといてくれるんすか〜。ありがたいっす〜。</t>
+          <t xml:space="preserve">あ〜、バレてました？ すんませ〜ん、明日から出まっす。</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
@@ -5341,14 +5341,14 @@
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">へぇ、別ルートっすか。下の子のケア助かります〜。</t>
+          <t xml:space="preserve">マジっすか〜、社長太っ腹！ 助かります〜。</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
@@ -5373,14 +5373,14 @@
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あー、はい〜、気をつけまーす。</t>
+          <t xml:space="preserve">へぇ、メンバーケアっすか〜。まあありがたいっす。</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
@@ -5405,14 +5405,14 @@
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（へらっと笑って、誤魔化した）</t>
+          <t xml:space="preserve">えへ、バレてました〜？ じゃお言葉に甘えて休みまっす。</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5427,7 +5427,7 @@
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
@@ -5437,14 +5437,14 @@
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">へぇ、別ルートっすか〜。まあ気持ちは受け取ります〜。</t>
+          <t xml:space="preserve">いやいや、まだいけますって〜。</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5459,7 +5459,7 @@
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
@@ -5469,14 +5469,14 @@
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えぇ〜、これくらいいけるんすけどな〜。はい、緩めまっす。</t>
+          <t xml:space="preserve">へぇ、メンバー優先っすか〜。助かりますね〜。</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
@@ -5501,14 +5501,14 @@
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お〜、続けていいんすか〜！ やった〜！</t>
+          <t xml:space="preserve">えー、そんな話してました？ まあ注意しときますんで〜。</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
@@ -5533,14 +5533,14 @@
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あれ、私じゃなくて子たち優先っすか〜？ まあありがたいっす。</t>
+          <t xml:space="preserve">お〜、放っといてくれるんすか〜。ありがたいっす〜。</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.easygoing.attack.delinquent</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5550,12 +5550,12 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.attack.delinquent</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
@@ -5565,14 +5565,14 @@
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲良しごっこは終わりだな</t>
+          <t xml:space="preserve">へぇ、別ルートっすか。下の子のケア助かります〜。</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.easygoing.defend.delinquent</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5582,12 +5582,12 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.defend.delinquent</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
@@ -5597,14 +5597,14 @@
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、しゃあねえな</t>
+          <t xml:space="preserve">あー、はい〜、気をつけまーす。</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5614,29 +5614,29 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おお！ なんかいつもと違うぜ！ いい感じ！</t>
+          <t xml:space="preserve">（へらっと笑って、誤魔化した）</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5646,29 +5646,29 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fresh.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お、今日は体が軽ぃな。もう一本いこうぜ</t>
+          <t xml:space="preserve">へぇ、別ルートっすか〜。まあ気持ちは受け取ります〜。</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5678,29 +5678,29 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heavy.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体がだりぃわ。今日やっても、ザルに水だろ</t>
+          <t xml:space="preserve">えぇ〜、これくらいいけるんすけどな〜。はい、緩めまっす。</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5710,29 +5710,29 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warm.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんか今日、乗んねーな。ま、動けてるからいっか</t>
+          <t xml:space="preserve">お〜、続けていいんすか〜！ やった〜！</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5742,29 +5742,29 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあいいや、ここまで来れただけでも上等だぜ</t>
+          <t xml:space="preserve">あれ、私じゃなくて子たち優先っすか〜？ まあありがたいっす。</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.easygoing.attack.delinquent</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5774,29 +5774,29 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">easygoing.attack.delinquent</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マジか、ここまで来ちゃったぜ！</t>
+          <t xml:space="preserve">仲良しごっこは終わりだな</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.easygoing.defend.delinquent</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5806,29 +5806,29 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">easygoing.defend.delinquent</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おー、いい感じに仕上がってきたぜ</t>
+          <t xml:space="preserve">ま、しゃあねえな</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -5853,14 +5853,14 @@
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うっひょー！ 最強じゃね？</t>
+          <t xml:space="preserve">おお！ なんかいつもと違うぜ！ いい感じ！</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5870,12 +5870,12 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">fresh.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -5885,14 +5885,14 @@
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高だぜ！ もっと声出せ〜！</t>
+          <t xml:space="preserve">お、今日は体が軽ぃな。もう一本いこうぜ</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[1]</t>
+          <t xml:space="preserve">heavy.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -5917,14 +5917,14 @@
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんだろうな…楽しいって感覚、どこ行っちまったんだ</t>
+          <t xml:space="preserve">体がだりぃわ。今日やっても、ザルに水だろ</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[1]</t>
+          <t xml:space="preserve">warm.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -5949,14 +5949,14 @@
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おっし、やる気出てきたぜ！ 楽しまねーとな</t>
+          <t xml:space="preserve">なんか今日、乗んねーな。ま、動けてるからいっか</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5966,12 +5966,12 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[1]</t>
+          <t xml:space="preserve">cap_reached.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -5981,14 +5981,14 @@
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いやー長かったな！ でもまた楽しくなってきたぜ</t>
+          <t xml:space="preserve">まあいいや、ここまで来れただけでも上等だぜ</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">ovr_elite.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -6013,14 +6013,14 @@
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんだろうな…いつもみたいに動かねーよ</t>
+          <t xml:space="preserve">マジか、ここまで来ちゃったぜ！</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">ovr_growth.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6045,14 +6045,14 @@
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あれ、治ったはずなのに調子でねーな</t>
+          <t xml:space="preserve">おー、いい感じに仕上がってきたぜ</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6062,12 +6062,12 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">ovr_legend.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6077,14 +6077,14 @@
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まいったな…リングがちょっと怖ぇーよ</t>
+          <t xml:space="preserve">うっひょー！ 最強じゃね？</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">pop_star.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6109,14 +6109,14 @@
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">怪我は治ったんだけどな…なんか乗んねーわ</t>
+          <t xml:space="preserve">最高だぜ！ もっと声出せ〜！</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6126,29 +6126,29 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">autumnWarChampion.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体戦って悪くないな。みんなで勝つと気分がいい。</t>
+          <t xml:space="preserve">なんだろうな…楽しいって感覚、どこ行っちまったんだ</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6158,29 +6158,29 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">終わった瞬間「もう1ラウンドくれ！」って叫びそうになった！</t>
+          <t xml:space="preserve">おっし、やる気出てきたぜ！ 楽しまねーとな</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6190,29 +6190,29 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンの響き、たまんねえ！ もっと楽しむぜ！</t>
+          <t xml:space="preserve">いやー長かったな！ でもまた楽しくなってきたぜ</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6222,29 +6222,29 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">defeat.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最っ高に楽しい選手人生だったぜ！ みんなありがとな！ プロレス最高！</t>
+          <t xml:space="preserve">なんだろうな…いつもみたいに動かねーよ</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6254,29 +6254,29 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うおお！ MVP！ いい響きじゃん！</t>
+          <t xml:space="preserve">あれ、治ったはずなのに調子でねーな</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6286,29 +6286,29 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うっそだろ！？ まあいいや、もらえるもんはもらっとく！</t>
+          <t xml:space="preserve">まいったな…リングがちょっと怖ぇーよ</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.springTagChampion.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6318,29 +6318,29 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">springTagChampion.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">penalty_end.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相棒となら、面倒な相手でもなんとかなるもんだな。</t>
+          <t xml:space="preserve">怪我は治ったんだけどな…なんか乗んねーわ</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[1]</t>
+          <t xml:space="preserve">autumnWarChampion.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6365,14 +6365,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おーっ、ドームか。まぁやるだけよ</t>
+          <t xml:space="preserve">団体戦って悪くないな。みんなで勝つと気分がいい。</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[2]</t>
+          <t xml:space="preserve">bestMatch.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6397,14 +6397,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんつーか、あんま緊張しねーな。やるべ</t>
+          <t xml:space="preserve">終わった瞬間「もう1ラウンドくれ！」って叫びそうになった！</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.delinquent.easygoing[3]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6414,12 +6414,12 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[3]</t>
+          <t xml:space="preserve">champion.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6429,14 +6429,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いつも通りだろ。気楽に行こうぜ</t>
+          <t xml:space="preserve">チャンピオンの響き、たまんねえ！ もっと楽しむぜ！</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6446,12 +6446,12 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[1]</t>
+          <t xml:space="preserve">hallOfFame.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6461,14 +6461,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マジで満員かよ！ やっべ、嬉しくて笑えてきたわ</t>
+          <t xml:space="preserve">最っ高に楽しい選手人生だったぜ！ みんなありがとな！ プロレス最高！</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6478,12 +6478,12 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[2]</t>
+          <t xml:space="preserve">mvp.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6493,14 +6493,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">観客全員ぶち上がってたな！ 気持ち良かったぜ</t>
+          <t xml:space="preserve">うおお！ MVP！ いい響きじゃん！</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.delinquent.easygoing[3]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[3]</t>
+          <t xml:space="preserve">rookie.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6525,14 +6525,14 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こういう日もあんだな、人生ってよ</t>
+          <t xml:space="preserve">うっそだろ！？ まあいいや、もらえるもんはもらっとく！</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6542,29 +6542,29 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">springTagChampion.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんか急にキタわ！掴めた感じ！</t>
+          <t xml:space="preserve">相棒となら、面倒な相手でもなんとかなるもんだな。</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6574,29 +6574,29 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あいつ最高！一緒だとテンション上がるわ！</t>
+          <t xml:space="preserve">おーっ、ドームか。まぁやるだけよ</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6606,29 +6606,29 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あー疲れた。ちょい休むわ</t>
+          <t xml:space="preserve">なんつーか、あんま緊張しねーな。やるべ</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.delinquent.easygoing[3]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6638,29 +6638,29 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[3]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンが盛り上がってんの最高じゃん！</t>
+          <t xml:space="preserve">いつも通りだろ。気楽に行こうぜ</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6670,29 +6670,29 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もーいいわ。考えさせてくれ</t>
+          <t xml:space="preserve">マジで満員かよ！ やっべ、嬉しくて笑えてきたわ</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6702,29 +6702,29 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あー…いや、なんでもねー。平気平気</t>
+          <t xml:space="preserve">観客全員ぶち上がってたな！ 気持ち良かったぜ</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.delinquent.easygoing[3]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6734,29 +6734,29 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[3]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やった！ラッキー！</t>
+          <t xml:space="preserve">こういう日もあんだな、人生ってよ</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6766,29 +6766,29 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">N1.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">合宿だー！ 盛り上がっていくぞー！</t>
+          <t xml:space="preserve">なんか急にキタわ！掴めた感じ！</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6798,29 +6798,29 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">N2.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見てくれてたんだ？ じゃ、もうちょいやるか！</t>
+          <t xml:space="preserve">あいつ最高！一緒だとテンション上がるわ！</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6830,29 +6830,29 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">N3.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おっしゃ！元気出た！やってやるわ！</t>
+          <t xml:space="preserve">あー疲れた。ちょい休むわ</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6862,29 +6862,29 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">N4.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えー。せっかく楽しくやってたのに</t>
+          <t xml:space="preserve">ファンが盛り上がってんの最高じゃん！</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6894,29 +6894,29 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">N5_low.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テレビ！？ みんな見てるー？</t>
+          <t xml:space="preserve">もーいいわ。考えさせてくれ</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6926,29 +6926,29 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">N5_warning.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うぇーい！飲むぞ〜！</t>
+          <t xml:space="preserve">あー…いや、なんでもねー。平気平気</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">bonus.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -6973,14 +6973,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">バカンスだー！戻ったら本気出すから！</t>
+          <t xml:space="preserve">やった！ラッキー！</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -6995,7 +6995,7 @@
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">camp.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7005,14 +7005,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マジか！すぐ治してくる！</t>
+          <t xml:space="preserve">合宿だー！ 盛り上がっていくぞー！</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">encourage_high_trust.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7037,14 +7037,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マンツーマン！？ 超贅沢じゃん！</t>
+          <t xml:space="preserve">見てくれてたんだ？ じゃ、もうちょいやるか！</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7054,12 +7054,12 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">encourage.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7069,14 +7069,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テレビ出んの！？ 最高じゃん！</t>
+          <t xml:space="preserve">おっしゃ！元気出た！やってやるわ！</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7086,12 +7086,12 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">faction_decree.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7101,14 +7101,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">他所から話来たんだけど！ちょっと嬉しくね？</t>
+          <t xml:space="preserve">えー。せっかく楽しくやってたのに</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">media.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7133,14 +7133,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はは…今日はサボるわ…</t>
+          <t xml:space="preserve">テレビ！？ みんな見てるー？</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7150,12 +7150,12 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">party.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7165,14 +7165,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習な…うーん、今日はパスで</t>
+          <t xml:space="preserve">うぇーい！飲むぞ〜！</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">refresh_leave.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7197,14 +7197,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（いつもの軽口が消え、「なぁ、ちょっとさぁ…」と珍しく愚痴をこぼしている）</t>
+          <t xml:space="preserve">バカンスだー！戻ったら本気出すから！</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">special_treatment.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7229,14 +7229,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに「最近ちょい考えることあってさ」と珍しく真面目な投稿）</t>
+          <t xml:space="preserve">マジか！すぐ治してくる！</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7246,12 +7246,12 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">trainer.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7261,14 +7261,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">タイトルマッチ組めよ！やる気あんだからさ！</t>
+          <t xml:space="preserve">マンツーマン！？ 超贅沢じゃん！</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7283,7 +7283,7 @@
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">E1.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7293,14 +7293,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あいつとやらせろよ！ケリつけてやる！</t>
+          <t xml:space="preserve">テレビ出んの！？ 最高じゃん！</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">E6.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7325,14 +7325,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">無理！限界！休ませて！</t>
+          <t xml:space="preserve">他所から話来たんだけど！ちょっと嬉しくね？</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7347,7 +7347,7 @@
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">S_boycott.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7357,14 +7357,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう無理！ちゃんと話し合えよ！</t>
+          <t xml:space="preserve">はは…今日はサボるわ…</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">S_boycott.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7389,14 +7389,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あー…いや、なんでもねえって（笑ってはいるが、目が笑っていない）</t>
+          <t xml:space="preserve">練習な…うーん、今日はパスで</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7411,7 +7411,7 @@
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">S_grumble.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7421,14 +7421,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">特訓すんぞ！もっと強くなりてーんだよ！</t>
+          <t xml:space="preserve">（いつもの軽口が消え、「なぁ、ちょっとさぁ…」と珍しく愚痴をこぼしている）</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">S_sns.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7453,14 +7453,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">後輩の面倒見るわ！任せとけ！</t>
+          <t xml:space="preserve">（SNSに「最近ちょい考えることあってさ」と珍しく真面目な投稿）</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7470,12 +7470,12 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">S1.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7485,14 +7485,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いった！やっちまったけど、すぐ治すから！</t>
+          <t xml:space="preserve">タイトルマッチ組めよ！やる気あんだからさ！</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">S2.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7517,14 +7517,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あいつマジ無理！もう顔も見たくねえ！</t>
+          <t xml:space="preserve">あいつとやらせろよ！ケリつけてやる！</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7534,12 +7534,12 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">S3.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7549,14 +7549,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やんのか！？ 売られたケンカは買うぜ！</t>
+          <t xml:space="preserve">無理！限界！休ませて！</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7566,12 +7566,12 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">S4_direct.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7581,14 +7581,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">コラボか。なんか面白そうじゃん</t>
+          <t xml:space="preserve">もう無理！ちゃんと話し合えよ！</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7598,12 +7598,12 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">S4_silent.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7613,14 +7613,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">CM撮影！？ 楽しそうじゃん！</t>
+          <t xml:space="preserve">あー…いや、なんでもねえって（笑ってはいるが、目が笑っていない）</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">S5.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7645,14 +7645,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンと直接会えるのいいじゃん！ 楽しみ！</t>
+          <t xml:space="preserve">特訓すんぞ！もっと強くなりてーんだよ！</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7662,12 +7662,12 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">S6.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7677,14 +7677,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ランウェイか。めっちゃ目立てそうじゃん！</t>
+          <t xml:space="preserve">後輩の面倒見るわ！任せとけ！</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7699,7 +7699,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">B1.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7709,14 +7709,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">グラビアか。まぁ、派手にやってやる</t>
+          <t xml:space="preserve">いった！やっちまったけど、すぐ治すから！</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">B2_fighter1.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7741,14 +7741,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テレビで暴れてやる！ 楽しみ！</t>
+          <t xml:space="preserve">あいつマジ無理！もう顔も見たくねえ！</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">B2_fighter2.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7773,14 +7773,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テレビ！？ マジ！？ やったー！</t>
+          <t xml:space="preserve">やんのか！？ 売られたケンカは買うぜ！</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7790,29 +7790,29 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[1]</t>
+          <t xml:space="preserve">B4_brand.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しくやろうぜ！退屈なのは嫌いだからな！</t>
+          <t xml:space="preserve">コラボか。なんか面白そうじゃん</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7822,29 +7822,29 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[1]</t>
+          <t xml:space="preserve">B4_cm.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よっ、よろしくな！ 楽しくやろうぜ</t>
+          <t xml:space="preserve">CM撮影！？ 楽しそうじゃん！</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7854,29 +7854,29 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[1]</t>
+          <t xml:space="preserve">B4_fan.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よっしゃー！新天地だ！暴れるぞ！</t>
+          <t xml:space="preserve">ファンと直接会えるのいいじゃん！ 楽しみ！</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7886,29 +7886,29 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[1]</t>
+          <t xml:space="preserve">B4_fashion.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よっしゃー！楽しくやろうぜ！</t>
+          <t xml:space="preserve">ランウェイか。めっちゃ目立てそうじゃん！</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7918,29 +7918,29 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[1]</t>
+          <t xml:space="preserve">B4_gravure.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やっちまったぜ〜 まぁすぐ戻るわ</t>
+          <t xml:space="preserve">グラビアか。まぁ、派手にやってやる</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7950,29 +7950,29 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">B4_variety.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しくやろうぜ！退屈なのは嫌いだからな！</t>
+          <t xml:space="preserve">テレビで暴れてやる！ 楽しみ！</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -7982,29 +7982,29 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">B4.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よっ、よろしくな！ 楽しくやろうぜ</t>
+          <t xml:space="preserve">テレビ！？ マジ！？ やったー！</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8014,12 +8014,12 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8029,14 +8029,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">フリーもそろそろ飽きたんでな。世話になるぜ</t>
+          <t xml:space="preserve">楽しくやろうぜ！退屈なのは嫌いだからな！</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8046,12 +8046,12 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8061,14 +8061,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よっしゃー！新天地だ！暴れるぞ！</t>
+          <t xml:space="preserve">よっ、よろしくな！ 楽しくやろうぜ</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8093,14 +8093,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よっしゃー！楽しくやろうぜ！</t>
+          <t xml:space="preserve">よっしゃー！新天地だ！暴れるぞ！</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8125,14 +8125,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お、今日は体が軽ぃな。もう一本いこうぜ</t>
+          <t xml:space="preserve">よっしゃー！楽しくやろうぜ！</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8157,14 +8157,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体がだりぃわ。今日やっても、ザルに水だろ</t>
+          <t xml:space="preserve">やっちまったぜ〜 まぁすぐ戻るわ</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">draftInterest.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8189,14 +8189,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんか今日、乗んねーな。ま、動けてるからいっか</t>
+          <t xml:space="preserve">楽しくやろうぜ！退屈なのは嫌いだからな！</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8211,7 +8211,7 @@
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">draftJoin.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8221,14 +8221,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やっちまったぜ〜 まぁすぐ戻るわ</t>
+          <t xml:space="preserve">よっ、よろしくな！ 楽しくやろうぜ</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8243,7 +8243,7 @@
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">faGreeting.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8253,14 +8253,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ、こんなもんか。元気でやれよ〜</t>
+          <t xml:space="preserve">フリーもそろそろ飽きたんでな。世話になるぜ</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8275,7 +8275,7 @@
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">faSigning.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8285,14 +8285,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おじゃまー！暴れさせてもらうぜ！</t>
+          <t xml:space="preserve">よっしゃー！新天地だ！暴れるぞ！</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">faWelcome.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8317,14 +8317,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">スカウトってのも、けっこう悪い気しねーな。やる気出てきたっ！</t>
+          <t xml:space="preserve">よっしゃー！楽しくやろうぜ！</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8339,7 +8339,7 @@
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8349,14 +8349,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそー！悔しい！でも次やってやるからな！</t>
+          <t xml:space="preserve">お、今日は体が軽ぃな。もう一本いこうぜ</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">heatSelf.heavy.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8381,14 +8381,14 @@
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだまだ渡さねーよ！最高！</t>
+          <t xml:space="preserve">体がだりぃわ。今日やっても、ザルに水だろ</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8403,7 +8403,7 @@
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">heatSelf.warm.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8413,14 +8413,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそー！でもまだ終わってねえから！</t>
+          <t xml:space="preserve">なんか今日、乗んねーな。ま、動けてるからいっか</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8435,7 +8435,7 @@
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">injury.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8445,14 +8445,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンだぜー！最高だろ！</t>
+          <t xml:space="preserve">やっちまったぜ〜 まぁすぐ戻るわ</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8462,12 +8462,12 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[1]</t>
+          <t xml:space="preserve">release.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8484,7 +8484,7 @@
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8494,12 +8494,12 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[1]</t>
+          <t xml:space="preserve">rentalGreeting.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8516,7 +8516,7 @@
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[1]</t>
+          <t xml:space="preserve">scoutGreeting.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8541,14 +8541,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそー！悔しい！でも次やってやるからな！</t>
+          <t xml:space="preserve">スカウトってのも、けっこう悪い気しねーな。やる気出てきたっ！</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8558,12 +8558,12 @@
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8573,14 +8573,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだまだ渡さねーよ！最高！</t>
+          <t xml:space="preserve">くそー！悔しい！でも次やってやるからな！</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="C260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[1]</t>
+          <t xml:space="preserve">titleDefense.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8605,14 +8605,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそー！でもまだ終わってねえから！</t>
+          <t xml:space="preserve">まだまだ渡さねーよ！最高！</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8622,12 +8622,12 @@
       </c>
       <c r="C261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[1]</t>
+          <t xml:space="preserve">titleLoss.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8637,14 +8637,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンだぜー！最高だろ！</t>
+          <t xml:space="preserve">くそー！でもまだ終わってねえから！</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8654,29 +8654,29 @@
       </c>
       <c r="C262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">titleWin.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う〜ん、ちょい合わねぇかもな…</t>
+          <t xml:space="preserve">チャンピオンだぜー！最高だろ！</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8686,29 +8686,29 @@
       </c>
       <c r="C263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あれ〜、最近ちょい素っ気なくね？</t>
+          <t xml:space="preserve">まぁ、こんなもんか。元気でやれよ〜</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8718,29 +8718,29 @@
       </c>
       <c r="C264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">んー、なんか空気変わった気ぃすんだけど</t>
+          <t xml:space="preserve">おじゃまー！暴れさせてもらうぜ！</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8750,29 +8750,29 @@
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">つるんでると楽しいんだわ、まじで</t>
+          <t xml:space="preserve">くそー！悔しい！でも次やってやるからな！</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8782,29 +8782,29 @@
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一生の仲間だぜ。間違いない</t>
+          <t xml:space="preserve">まだまだ渡さねーよ！最高！</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8814,29 +8814,29 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">熱い関係も一段落かぁ。ちっと寂しいな</t>
+          <t xml:space="preserve">くそー！でもまだ終わってねえから！</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8846,29 +8846,29 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ因縁も永遠じゃねぇよな〜</t>
+          <t xml:space="preserve">チャンピオンだぜー！最高だろ！</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8883,7 +8883,7 @@
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">bond_39_down.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -8893,14 +8893,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やり合うの、ワクワクすんだよな</t>
+          <t xml:space="preserve">う〜ん、ちょい合わねぇかもな…</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8915,7 +8915,7 @@
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">bond_59_down.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -8925,14 +8925,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">本気でやり合いてぇ相手なんて、そうはいねぇよ</t>
+          <t xml:space="preserve">あれ〜、最近ちょい素っ気なくね？</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">bond_59_down.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -8957,14 +8957,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">へへ、考えると自然に気合入るんだわ</t>
+          <t xml:space="preserve">んー、なんか空気変わった気ぃすんだけど</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -8979,7 +8979,7 @@
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">bond_60_up.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -8989,14 +8989,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この試合が一番楽しいんだわ。ずっと続けばいいのにな</t>
+          <t xml:space="preserve">つるんでると楽しいんだわ、まじで</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9011,7 +9011,7 @@
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">bond_80_up.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9021,14 +9021,14 @@
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">運命のライバルってやつだろ。最高だぜ</t>
+          <t xml:space="preserve">一生の仲間だぜ。間違いない</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9043,7 +9043,7 @@
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">rivalry_29_down.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9053,14 +9053,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここ最高〜！ みんなとやんの楽しいわ！</t>
+          <t xml:space="preserve">熱い関係も一段落かぁ。ちっと寂しいな</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9075,7 +9075,7 @@
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">rivalry_29_down.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9085,14 +9085,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体、すげぇ居心地いいんだわ〜</t>
+          <t xml:space="preserve">まぁ因縁も永遠じゃねぇよな〜</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9107,7 +9107,7 @@
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">rivalry_30_up.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9117,14 +9117,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">さすがにこれは…笑えねぇかも</t>
+          <t xml:space="preserve">やり合うの、ワクワクすんだよな</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">rivalry_50_up.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9149,14 +9149,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あはは…って笑ってる場合じゃねぇよな、これ</t>
+          <t xml:space="preserve">本気でやり合いてぇ相手なんて、そうはいねぇよ</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.easygoing.delinquent[1]</t>
+          <t xml:space="preserve">rivalry_50_up.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9181,14 +9181,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う〜ん、最近ちっとモヤモヤすんだよなぁ…</t>
+          <t xml:space="preserve">へへ、考えると自然に気合入るんだわ</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9203,7 +9203,7 @@
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.easygoing.delinquent[2]</t>
+          <t xml:space="preserve">rivalry_70_up.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9213,14 +9213,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ大丈夫…だよな？ ちょい不安だけど</t>
+          <t xml:space="preserve">この試合が一番楽しいんだわ。ずっと続けばいいのにな</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[1]</t>
+          <t xml:space="preserve">rivalry_70_up.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9245,14 +9245,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">終わっちまったかー。まぁ次また来るっしょ</t>
+          <t xml:space="preserve">運命のライバルってやつだろ。最高だぜ</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9262,29 +9262,29 @@
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">trust_above_75.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いやー身体ガタガタだわ。でも最後だし、暴れて終わろうぜ</t>
+          <t xml:space="preserve">ここ最高〜！ みんなとやんの楽しいわ！</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9294,29 +9294,29 @@
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">trust_above_75.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで残っちまったな。ま、痛いのは後で考えるわ</t>
+          <t xml:space="preserve">この団体、すげぇ居心地いいんだわ〜</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9326,29 +9326,29 @@
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">trust_below_20.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手は誰だ？ ま、来た奴から順にぶっ倒すだけだ</t>
+          <t xml:space="preserve">さすがにこれは…笑えねぇかも</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9358,29 +9358,29 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">trust_below_20.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いいぜいいぜ、次々来いよ。まとめて相手してやるって</t>
+          <t xml:space="preserve">あはは…って笑ってる場合じゃねぇよな、これ</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9390,29 +9390,29 @@
       </c>
       <c r="C285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">trust_below_35.easygoing.delinquent[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人ぶっ倒したー！ …はぁ、まだいけるっしょ。次、出てこいよー</t>
+          <t xml:space="preserve">う〜ん、最近ちっとモヤモヤすんだよなぁ…</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9422,29 +9422,29 @@
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">trust_below_35.easygoing.delinquent[2]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふう、一丁上がり。でもまだ終わってねえぞ。次、さっさと来い</t>
+          <t xml:space="preserve">まぁ大丈夫…だよな？ ちょい不安だけど</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9454,29 +9454,29 @@
       </c>
       <c r="C287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で勝ったぜ！ いやー、最高の気分だな</t>
+          <t xml:space="preserve">終わっちまったかー。まぁ次また来るっしょ</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9486,12 +9486,12 @@
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">preFinal.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9501,14 +9501,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間がいたから全然余裕だったっての。まあ、ちょっとは焦ったけどな</t>
+          <t xml:space="preserve">いやー身体ガタガタだわ。でも最後だし、暴れて終わろうぜ</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9518,12 +9518,12 @@
       </c>
       <c r="C289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">preFinal.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9533,14 +9533,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVPねえ。まあもらっとくけどさ、一人じゃ盛り上がんねえよ</t>
+          <t xml:space="preserve">ここまで残っちまったな。ま、痛いのは後で考えるわ</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9550,12 +9550,12 @@
       </c>
       <c r="C290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">preMatch.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9565,14 +9565,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次は全員で暴れて、全員で勝つ。そうじゃなきゃつまんねえ</t>
+          <t xml:space="preserve">相手は誰だ？ ま、来た奴から順にぶっ倒すだけだ</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9582,12 +9582,12 @@
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">preMatch.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9597,14 +9597,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いやー次から次に来んのな。途中から面白くなっちゃったよ</t>
+          <t xml:space="preserve">いいぜいいぜ、次々来いよ。まとめて相手してやるって</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9614,12 +9614,12 @@
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">survivor.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9629,14 +9629,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人だっけ？ まあいいや、全員倒したし。私の勝ちってことで</t>
+          <t xml:space="preserve">一人ぶっ倒したー！ …はぁ、まだいけるっしょ。次、出てこいよー</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9646,12 +9646,12 @@
       </c>
       <c r="C293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">survivor.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9661,14 +9661,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いえ〜い！ 優勝〜！ 最高じゃん！</t>
+          <t xml:space="preserve">ふう、一丁上がり。でもまだ終わってねえぞ。次、さっさと来い</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9678,12 +9678,12 @@
       </c>
       <c r="C294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">champion.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9693,14 +9693,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ひゃっほ〜！ やったぜ〜！</t>
+          <t xml:space="preserve">三人で勝ったぜ！ いやー、最高の気分だな</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9710,12 +9710,12 @@
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">champion.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9725,14 +9725,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マジかー、負けたわ。ま、次があるし</t>
+          <t xml:space="preserve">仲間がいたから全然余裕だったっての。まあ、ちょっとは焦ったけどな</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9742,12 +9742,12 @@
       </c>
       <c r="C296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">defiant.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9757,14 +9757,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">しゃーねえな。次だ次</t>
+          <t xml:space="preserve">MVPねえ。まあもらっとくけどさ、一人じゃ盛り上がんねえよ</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9774,12 +9774,12 @@
       </c>
       <c r="C297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">defiant.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9789,14 +9789,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いえーい！ 楽勝楽勝〜</t>
+          <t xml:space="preserve">次は全員で暴れて、全員で勝つ。そうじゃなきゃつまんねえ</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9806,12 +9806,12 @@
       </c>
       <c r="C298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">gauntlet.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9821,14 +9821,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ノリノリだぜ！ 次も行くぞ〜</t>
+          <t xml:space="preserve">いやー次から次に来んのな。途中から面白くなっちゃったよ</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9838,12 +9838,12 @@
       </c>
       <c r="C299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">gauntlet.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9853,14 +9853,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しかったぜ〜。またやりてえな</t>
+          <t xml:space="preserve">何人だっけ？ まあいいや、全員倒したし。私の勝ちってことで</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9875,7 +9875,7 @@
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">champion.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -9885,14 +9885,14 @@
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあまあ良かったんじゃね？</t>
+          <t xml:space="preserve">いえ〜い！ 優勝〜！ 最高じゃん！</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">champion.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -9917,14 +9917,14 @@
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うっひょ〜決勝じゃん！ やるっきゃねえ！</t>
+          <t xml:space="preserve">ひゃっほ〜！ やったぜ〜！</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">postLose.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -9949,14 +9949,14 @@
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最後だし、全力で暴れるぜ！</t>
+          <t xml:space="preserve">マジかー、負けたわ。ま、次があるし</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -9971,7 +9971,7 @@
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">postLose.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
@@ -9981,14 +9981,14 @@
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よーし、パパッとやっちまうか</t>
+          <t xml:space="preserve">しゃーねえな。次だ次</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10003,7 +10003,7 @@
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">postMatchWin.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
@@ -10013,14 +10013,14 @@
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">気楽にいこうぜ。でも手は抜かねえけど</t>
+          <t xml:space="preserve">いえーい！ 楽勝楽勝〜</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10035,7 +10035,7 @@
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">postMatchWin.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
@@ -10045,14 +10045,14 @@
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マジ？ ウケる。まあ出てやるよ</t>
+          <t xml:space="preserve">ノリノリだぜ！ 次も行くぞ〜</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10067,7 +10067,7 @@
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">postWin.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
@@ -10077,14 +10077,14 @@
       </c>
       <c r="F306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、暴れる場所があるなら出るっしょ</t>
+          <t xml:space="preserve">楽しかったぜ〜。またやりてえな</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10094,12 +10094,12 @@
       </c>
       <c r="C307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[1]</t>
+          <t xml:space="preserve">postWin.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
@@ -10109,14 +10109,14 @@
       </c>
       <c r="F307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高だぜ！楽しもうや！</t>
+          <t xml:space="preserve">まあまあ良かったんじゃね？</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10126,12 +10126,12 @@
       </c>
       <c r="C308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[2]</t>
+          <t xml:space="preserve">preFinal.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
@@ -10141,14 +10141,14 @@
       </c>
       <c r="F308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">へぇ、派手な舞台じゃん！せっかくだし楽しもっかな！</t>
+          <t xml:space="preserve">うっひょ〜決勝じゃん！ やるっきゃねえ！</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="C309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[1]</t>
+          <t xml:space="preserve">preFinal.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
@@ -10173,14 +10173,14 @@
       </c>
       <c r="F309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マジかよ……！ やべえ、勝っちまった……！ 最高だ！</t>
+          <t xml:space="preserve">最後だし、全力で暴れるぜ！</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="C310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[1]</t>
+          <t xml:space="preserve">preMatch.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
@@ -10205,14 +10205,14 @@
       </c>
       <c r="F310" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よう、暇だから殴りに来たぜ</t>
+          <t xml:space="preserve">よーし、パパッとやっちまうか</t>
         </is>
       </c>
     </row>
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="C311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[2]</t>
+          <t xml:space="preserve">preMatch.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="2">
@@ -10237,14 +10237,14 @@
       </c>
       <c r="F311" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">面白えことしようぜ。対抗戦だ対抗戦</t>
+          <t xml:space="preserve">気楽にいこうぜ。でも手は抜かねえけど</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10254,12 +10254,12 @@
       </c>
       <c r="C312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[1]</t>
+          <t xml:space="preserve">summon.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
@@ -10269,14 +10269,14 @@
       </c>
       <c r="F312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">は？ 逃げんの？ ダッセー</t>
+          <t xml:space="preserve">マジ？ ウケる。まあ出てやるよ</t>
         </is>
       </c>
     </row>
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="C313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[2]</t>
+          <t xml:space="preserve">summon.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
@@ -10301,14 +10301,14 @@
       </c>
       <c r="F313" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、ビビるのもわかるけどな。またな</t>
+          <t xml:space="preserve">ま、暴れる場所があるなら出るっしょ</t>
         </is>
       </c>
     </row>
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="C314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E314" t="inlineStr" s="2">
@@ -10333,14 +10333,14 @@
       </c>
       <c r="F314" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、こういう日もあるっしょ。次だ次！</t>
+          <t xml:space="preserve">最高だぜ！楽しもうや！</t>
         </is>
       </c>
     </row>
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10350,12 +10350,12 @@
       </c>
       <c r="C315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D315" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E315" t="inlineStr" s="2">
@@ -10365,14 +10365,14 @@
       </c>
       <c r="F315" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くっそー、やられた。次は倍返しだ</t>
+          <t xml:space="preserve">へぇ、派手な舞台じゃん！せっかくだし楽しもっかな！</t>
         </is>
       </c>
     </row>
     <row r="316" ht="40" customHeight="1">
       <c r="A316" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
@@ -10382,12 +10382,12 @@
       </c>
       <c r="C316" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D316" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E316" t="inlineStr" s="2">
@@ -10397,14 +10397,14 @@
       </c>
       <c r="F316" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いえーい！ 圧勝だぜ〜！</t>
+          <t xml:space="preserve">マジかよ……！ やべえ、勝っちまった……！ 最高だ！</t>
         </is>
       </c>
     </row>
     <row r="317" ht="40" customHeight="1">
       <c r="A317" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
@@ -10414,12 +10414,12 @@
       </c>
       <c r="C317" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D317" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E317" t="inlineStr" s="2">
@@ -10429,14 +10429,14 @@
       </c>
       <c r="F317" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">面白かったぜ！ またかかって来いよ</t>
+          <t xml:space="preserve">よう、暇だから殴りに来たぜ</t>
         </is>
       </c>
     </row>
     <row r="318" ht="40" customHeight="1">
       <c r="A318" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B318" t="inlineStr" s="2">
@@ -10446,12 +10446,12 @@
       </c>
       <c r="C318" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D318" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[1]</t>
+          <t xml:space="preserve">delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E318" t="inlineStr" s="2">
@@ -10461,14 +10461,14 @@
       </c>
       <c r="F318" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よっしゃあ！ 勝った勝った！ 打ち上げだ打ち上げ！</t>
+          <t xml:space="preserve">面白えことしようぜ。対抗戦だ対抗戦</t>
         </is>
       </c>
     </row>
     <row r="319" ht="40" customHeight="1">
       <c r="A319" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.easygoing[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B319" t="inlineStr" s="2">
@@ -10478,12 +10478,12 @@
       </c>
       <c r="C319" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D319" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[2]</t>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E319" t="inlineStr" s="2">
@@ -10493,14 +10493,14 @@
       </c>
       <c r="F319" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よっしゃ〜！ まだまだいけるぜ〜！</t>
+          <t xml:space="preserve">は？ 逃げんの？ ダッセー</t>
         </is>
       </c>
     </row>
     <row r="320" ht="40" customHeight="1">
       <c r="A320" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.easygoing[3]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B320" t="inlineStr" s="2">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="C320" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D320" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[3]</t>
+          <t xml:space="preserve">delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E320" t="inlineStr" s="2">
@@ -10525,14 +10525,14 @@
       </c>
       <c r="F320" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いえーい！ 圧勝〜！ 打ち上げ行くぞ〜！</t>
+          <t xml:space="preserve">ま、ビビるのもわかるけどな。またな</t>
         </is>
       </c>
     </row>
     <row r="321" ht="40" customHeight="1">
       <c r="A321" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="B321" t="inlineStr" s="2">
@@ -10542,29 +10542,29 @@
       </c>
       <c r="C321" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D321" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">result_lose.delinquent.easygoing[1]</t>
         </is>
       </c>
       <c r="E321" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F321" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高だぜ！みんなありがとな！</t>
+          <t xml:space="preserve">ま、こういう日もあるっしょ。次だ次！</t>
         </is>
       </c>
     </row>
     <row r="322" ht="40" customHeight="1">
       <c r="A322" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.delinquent.easygoing[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="B322" t="inlineStr" s="2">
@@ -10574,59 +10574,283 @@
       </c>
       <c r="C322" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D322" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.easygoing[1]</t>
+          <t xml:space="preserve">result_lose.delinquent.easygoing[2]</t>
         </is>
       </c>
       <c r="E322" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F322" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">フリーもそろそろ飽きたんでな。世話になるぜ</t>
+          <t xml:space="preserve">くっそー、やられた。次は倍返しだ</t>
         </is>
       </c>
     </row>
     <row r="323" ht="40" customHeight="1">
       <c r="A323" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">いえーい！ 圧勝だぜ〜！</t>
+        </is>
+      </c>
+    </row>
+    <row r="324" ht="40" customHeight="1">
+      <c r="A324" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.delinquent.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.delinquent.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">面白かったぜ！ またかかって来いよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="325" ht="40" customHeight="1">
+      <c r="A325" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">よっしゃあ！ 勝った勝った！ 打ち上げだ打ち上げ！</t>
+        </is>
+      </c>
+    </row>
+    <row r="326" ht="40" customHeight="1">
+      <c r="A326" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">delinquent.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">よっしゃ〜！ まだまだいけるぜ〜！</t>
+        </is>
+      </c>
+    </row>
+    <row r="327" ht="40" customHeight="1">
+      <c r="A327" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.easygoing[3]</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">delinquent.easygoing[3]</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">いえーい！ 圧勝〜！ 打ち上げ行くぞ〜！</t>
+        </is>
+      </c>
+    </row>
+    <row r="328" ht="40" customHeight="1">
+      <c r="A328" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">最高だぜ！みんなありがとな！</t>
+        </is>
+      </c>
+    </row>
+    <row r="329" ht="40" customHeight="1">
+      <c r="A329" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">delinquent.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">フリーもそろそろ飽きたんでな。世話になるぜ</t>
+        </is>
+      </c>
+    </row>
+    <row r="330" ht="40" customHeight="1">
+      <c r="A330" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.delinquent.easygoing[1]</t>
         </is>
       </c>
-      <c r="B323" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C323" t="inlineStr" s="2">
+      <c r="B330" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D323" t="inlineStr" s="12">
+      <c r="D330" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">delinquent.easygoing[1]</t>
         </is>
       </c>
-      <c r="E323" t="inlineStr" s="2">
+      <c r="E330" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F323" t="inlineStr" s="3">
+      <c r="F330" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">スカウトってのも、けっこう悪い気しねーな。やる気出てきたっ！</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H323"/>
+  <autoFilter ref="A1:H330"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/ヤンキー×お気楽.xlsx
+++ b/セリフ編集/キャラタイプ別/ヤンキー×お気楽.xlsx
@@ -2393,7 +2393,7 @@
       </c>
       <c r="F66" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、あの人とやらせてよ。頼む。</t>
+          <t xml:space="preserve">社長、三人であっちへ行かせてよ。頼む。</t>
         </is>
       </c>
     </row>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="F67" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やりたい相手がいるんだ。組んでくれ。</t>
+          <t xml:space="preserve">やりたい団体があるんだ。三人で組んでくれ。</t>
         </is>
       </c>
     </row>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="F68" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なあ社長、あの人と当ててくれない？</t>
+          <t xml:space="preserve">なあ社長、三人であの団体に当ててくれない？</t>
         </is>
       </c>
     </row>
